--- a/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="92">
   <si>
     <t>ARHS</t>
   </si>
@@ -656,184 +656,190 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>344000</v>
+      </c>
+      <c r="E8" s="3">
         <v>326200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>312900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>304600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>356300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>320000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>306300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>246300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>238200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>203300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>184000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>171300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>162800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>120500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>103400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>120700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>133800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>202800</v>
+      </c>
+      <c r="E9" s="3">
         <v>195400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>172800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>176300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>198300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>183700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>173200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>148600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>141300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>118500</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
@@ -855,41 +861,44 @@
       <c r="T9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>141200</v>
+      </c>
+      <c r="E10" s="3">
         <v>130800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>140100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>128300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>158000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>136300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>133100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>97700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>96900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>84800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -911,8 +920,11 @@
       <c r="T10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +945,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,13 +1061,16 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1059,11 +1078,11 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
@@ -1071,12 +1090,12 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>1500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1089,8 +1108,8 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1101,16 +1120,19 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>700</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>500</v>
       </c>
       <c r="F15" s="3">
         <v>500</v>
@@ -1127,8 +1149,8 @@
       <c r="J15" s="3">
         <v>500</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
+      <c r="K15" s="3">
+        <v>500</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>5</v>
@@ -1145,8 +1167,8 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1157,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,41 +1201,42 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>303000</v>
+      </c>
+      <c r="E17" s="3">
         <v>302300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>258900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>259100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>291900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>272900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>256000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>223400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>242600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>186700</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1226,47 +1252,50 @@
       <c r="R17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
+      <c r="S17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E18" s="3">
         <v>23900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>54000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>45500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>64400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>47100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>50300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>22900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>16600</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1282,14 +1311,17 @@
       <c r="R18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>133800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,41 +1342,42 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E20" s="3">
         <v>2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>400</v>
       </c>
       <c r="L20" s="3">
+        <v>400</v>
+      </c>
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1360,47 +1393,50 @@
       <c r="R20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>-130800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-121600</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E21" s="3">
         <v>33800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>63300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>54300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>71700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>53600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>56500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>29100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>24500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1422,8 +1458,11 @@
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1431,28 +1470,28 @@
         <v>1400</v>
       </c>
       <c r="E22" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="F22" s="3">
         <v>1300</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>800</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1300</v>
       </c>
       <c r="J22" s="3">
         <v>1300</v>
       </c>
       <c r="K22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L22" s="3">
         <v>1400</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1300</v>
       </c>
       <c r="M22" s="3">
         <v>1300</v>
@@ -1461,58 +1500,61 @@
         <v>1300</v>
       </c>
       <c r="O22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P22" s="3">
         <v>3200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3600</v>
-      </c>
-      <c r="R22" s="3">
-        <v>3000</v>
       </c>
       <c r="S22" s="3">
         <v>3000</v>
       </c>
       <c r="T22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="U22" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E23" s="3">
         <v>25000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>54600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>46200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>65100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>46500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>49100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14900</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1528,58 +1570,61 @@
       <c r="R23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
+      <c r="S23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E24" s="3">
         <v>5300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>18100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-11800</v>
-      </c>
-      <c r="L24" s="3">
-        <v>500</v>
       </c>
       <c r="M24" s="3">
         <v>500</v>
       </c>
       <c r="N24" s="3">
+        <v>500</v>
+      </c>
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>100</v>
       </c>
       <c r="R24" s="3">
         <v>100</v>
@@ -1588,10 +1633,13 @@
         <v>100</v>
       </c>
       <c r="T24" s="3">
+        <v>100</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,41 +1694,44 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E26" s="3">
         <v>19700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>40200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>34100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>47000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>36900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>36600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14400</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1696,47 +1747,50 @@
       <c r="R26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
+      <c r="S26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E27" s="3">
         <v>19700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>40200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>34100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>47000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>36900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>36600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14400</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1752,14 +1806,17 @@
       <c r="R27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
+      <c r="S27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,41 +2048,44 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>-400</v>
       </c>
       <c r="L32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2032,47 +2101,50 @@
       <c r="R32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>130800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E33" s="3">
         <v>19700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>40200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>34100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>47000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>36900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>36600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14400</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>5</v>
       </c>
@@ -2088,14 +2160,17 @@
       <c r="R33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
+      <c r="S33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,41 +2225,44 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E35" s="3">
         <v>19700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>40200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>34100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>47000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>36900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>36600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14400</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>5</v>
       </c>
@@ -2200,75 +2278,81 @@
       <c r="R35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
+      <c r="S35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,44 +2396,45 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>223100</v>
+      </c>
+      <c r="E41" s="3">
         <v>236900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>176800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>144500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>145200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>145700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>144600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>148800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>123800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>149200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>132900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2367,8 +2453,11 @@
       <c r="T41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,44 +2512,47 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E43" s="3">
         <v>2000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>500</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2479,44 +2571,47 @@
       <c r="T43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>254300</v>
+      </c>
+      <c r="E44" s="3">
         <v>269000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>294900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>292100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>286400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>292600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>272500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>246500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>208300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>170600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>136100</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2535,44 +2630,47 @@
       <c r="T44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E45" s="3">
         <v>66600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>47700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>51200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>44700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>42200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>36500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>38100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>26300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>21700</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2591,44 +2689,47 @@
       <c r="T45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>528300</v>
+      </c>
+      <c r="E46" s="3">
         <v>574500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>521000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>489800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>478100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>482300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>455100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>435100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>368000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>346400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>291300</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2647,8 +2748,11 @@
       <c r="T46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2703,44 +2807,47 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>551200</v>
+      </c>
+      <c r="E48" s="3">
         <v>510500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>498700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>452600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>425600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>392800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>387900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>342600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>179600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>137000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>123600</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
@@ -2759,8 +2866,11 @@
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2794,8 +2904,8 @@
       <c r="M49" s="3">
         <v>11000</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
+      <c r="N49" s="3">
+        <v>11000</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>5</v>
@@ -2815,8 +2925,11 @@
       <c r="T49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,44 +3043,47 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E52" s="3">
         <v>19700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>23100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2983,8 +3102,11 @@
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,44 +3161,47 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1114100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1115600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1045300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>965900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>931800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>907200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>877000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>814200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>586600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>495300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>426800</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3095,8 +3220,11 @@
       <c r="T54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,44 +3268,45 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E57" s="3">
         <v>58100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>55100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>53100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>62600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>58500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>62300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>54200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>51400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>30400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>30000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3195,8 +3325,11 @@
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3207,7 +3340,7 @@
         <v>900</v>
       </c>
       <c r="F58" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="G58" s="3">
         <v>500</v>
@@ -3219,20 +3352,20 @@
         <v>500</v>
       </c>
       <c r="J58" s="3">
+        <v>500</v>
+      </c>
+      <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N58" s="3">
         <v>200</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3251,44 +3384,47 @@
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>286700</v>
+      </c>
+      <c r="E59" s="3">
         <v>327100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>288600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>293300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>310600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>365000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>363800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>390500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>349800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>306400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>259000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3307,44 +3443,47 @@
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>351300</v>
+      </c>
+      <c r="E60" s="3">
         <v>386200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>344600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>346800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>373800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>424000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>426700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>444900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>401200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>336700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>289200</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>5</v>
       </c>
@@ -3363,44 +3502,47 @@
       <c r="T60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E61" s="3">
         <v>54000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>53900</v>
-      </c>
-      <c r="F61" s="3">
-        <v>51800</v>
       </c>
       <c r="G61" s="3">
         <v>51800</v>
       </c>
       <c r="H61" s="3">
+        <v>51800</v>
+      </c>
+      <c r="I61" s="3">
         <v>51900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>52000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>50300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>50500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>47800</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3419,44 +3561,47 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>368700</v>
+      </c>
+      <c r="E62" s="3">
         <v>366900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>359200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>322200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>296500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>270500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>274500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>232400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>65000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>127800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>124800</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3475,8 +3620,11 @@
       <c r="T62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,44 +3797,47 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>773900</v>
+      </c>
+      <c r="E66" s="3">
         <v>807100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>757700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>720800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>722100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>746400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>753100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>727600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>516800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>515100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>461700</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>5</v>
       </c>
@@ -3699,8 +3856,11 @@
       <c r="T66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,44 +4115,47 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>145300</v>
+      </c>
+      <c r="E72" s="3">
         <v>114100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>94300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>54200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>20100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-26900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-63900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-100500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-116600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-22700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-37000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4001,8 +4174,11 @@
       <c r="T72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,44 +4351,47 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>340200</v>
+      </c>
+      <c r="E76" s="3">
         <v>308500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>287600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>245100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>209700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>160800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>123900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>86500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>69800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-19800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-34900</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>5</v>
       </c>
@@ -4225,8 +4410,11 @@
       <c r="T76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,102 +4469,108 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E81" s="3">
         <v>19700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>40200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>34100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>47000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>36900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>36600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14400</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>5</v>
       </c>
@@ -4392,14 +4586,17 @@
       <c r="R81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
+      <c r="S81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,50 +4617,51 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E83" s="3">
         <v>7300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>17000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>5</v>
       </c>
@@ -4476,8 +4674,11 @@
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,50 +4969,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E89" s="3">
         <v>69600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>54100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>16200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>35200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>31800</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
         <v>150400</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>5</v>
       </c>
@@ -4812,8 +5028,11 @@
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,50 +5053,51 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-24300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8500</v>
       </c>
-      <c r="G91" s="3">
-        <v>-15700</v>
-      </c>
       <c r="H91" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-16600</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-10200</v>
       </c>
       <c r="J91" s="3">
         <v>-10200</v>
       </c>
       <c r="K91" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="L91" s="3">
         <v>-18300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15800</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3">
         <v>-13000</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>5</v>
       </c>
@@ -4890,8 +5110,11 @@
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,50 +5228,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-24300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-15700</v>
-      </c>
       <c r="H94" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="I94" s="3">
         <v>-16600</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-10200</v>
       </c>
       <c r="J94" s="3">
         <v>-10200</v>
       </c>
       <c r="K94" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="L94" s="3">
         <v>-18300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15800</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-13000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>5</v>
       </c>
@@ -5058,8 +5287,11 @@
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5312,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,50 +5546,53 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-100</v>
       </c>
       <c r="H100" s="3">
         <v>-100</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-15900</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
+      <c r="M100" s="3">
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>-98300</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>5</v>
       </c>
@@ -5360,8 +5605,11 @@
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5416,50 +5664,53 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E102" s="3">
         <v>59000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>29700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>25100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-30600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>16000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>39100</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>5</v>
       </c>
@@ -5470,6 +5721,9 @@
         <v>5</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="92">
   <si>
     <t>ARHS</t>
   </si>
@@ -656,193 +656,200 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>295200</v>
+      </c>
+      <c r="E8" s="3">
         <v>344000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>326200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>312900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>304600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>356300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>320000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>306300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>246300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>238200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>203300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>184000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>171300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>162800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>120500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>103400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>120700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>133800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>180100</v>
+      </c>
+      <c r="E9" s="3">
         <v>202800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>195400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>172800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>176300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>198300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>183700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>173200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>148600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>141300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>118500</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
@@ -864,44 +871,47 @@
       <c r="U9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>115100</v>
+      </c>
+      <c r="E10" s="3">
         <v>141200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>130800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>140100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>128300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>158000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>136300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>133100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>97700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>96900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>84800</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
@@ -923,8 +933,11 @@
       <c r="U10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1005,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,16 +1081,19 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
@@ -1081,11 +1101,11 @@
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
@@ -1093,12 +1113,12 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>1500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1111,8 +1131,8 @@
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1123,19 +1143,22 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>500</v>
       </c>
       <c r="G15" s="3">
         <v>500</v>
@@ -1152,8 +1175,8 @@
       <c r="K15" s="3">
         <v>500</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>5</v>
+      <c r="L15" s="3">
+        <v>500</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>5</v>
@@ -1170,8 +1193,8 @@
       <c r="Q15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,44 +1228,45 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>276800</v>
+      </c>
+      <c r="E17" s="3">
         <v>303000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>302300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>258900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>259100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>291900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>272900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>256000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>223400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>242600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>186700</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1255,50 +1282,53 @@
       <c r="S17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
+      <c r="T17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E18" s="3">
         <v>41000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>23900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>54000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>45500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>64400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>47100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>50300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>22900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>16600</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1314,14 +1344,17 @@
       <c r="S18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="3">
         <v>133800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,44 +1376,45 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E20" s="3">
         <v>3300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
       </c>
       <c r="J20" s="3">
         <v>100</v>
       </c>
       <c r="K20" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>400</v>
       </c>
       <c r="M20" s="3">
+        <v>400</v>
+      </c>
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1396,50 +1430,53 @@
       <c r="S20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="3">
         <v>-130800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-121600</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E21" s="3">
         <v>52300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>33800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>63300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>54300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>71700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>53600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>56500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>29100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>24500</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1461,8 +1498,11 @@
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1473,28 +1513,28 @@
         <v>1400</v>
       </c>
       <c r="F22" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G22" s="3">
         <v>1300</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>800</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1300</v>
       </c>
       <c r="K22" s="3">
         <v>1300</v>
       </c>
       <c r="L22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M22" s="3">
         <v>1400</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1300</v>
       </c>
       <c r="N22" s="3">
         <v>1300</v>
@@ -1503,61 +1543,64 @@
         <v>1300</v>
       </c>
       <c r="P22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q22" s="3">
         <v>3200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3600</v>
-      </c>
-      <c r="S22" s="3">
-        <v>3000</v>
       </c>
       <c r="T22" s="3">
         <v>3000</v>
       </c>
       <c r="U22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="V22" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E23" s="3">
         <v>42900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>25000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>54600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>46200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>65100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>46500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>49100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14900</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1573,61 +1616,64 @@
       <c r="S23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
+      <c r="T23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E24" s="3">
         <v>11700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>18100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-11800</v>
-      </c>
-      <c r="M24" s="3">
-        <v>500</v>
       </c>
       <c r="N24" s="3">
         <v>500</v>
       </c>
       <c r="O24" s="3">
+        <v>500</v>
+      </c>
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
-      </c>
-      <c r="R24" s="3">
-        <v>100</v>
       </c>
       <c r="S24" s="3">
         <v>100</v>
@@ -1636,10 +1682,13 @@
         <v>100</v>
       </c>
       <c r="U24" s="3">
+        <v>100</v>
+      </c>
+      <c r="V24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,44 +1746,47 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E26" s="3">
         <v>31200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>19700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>40200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>34100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>47000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>36900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>36600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14400</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1750,50 +1802,53 @@
       <c r="S26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
+      <c r="T26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E27" s="3">
         <v>31200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>40200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>34100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>47000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>36900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>36600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14400</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1809,14 +1864,17 @@
       <c r="S27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
+      <c r="T27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,44 +2118,47 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
       </c>
       <c r="J32" s="3">
         <v>-100</v>
       </c>
       <c r="K32" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-400</v>
       </c>
       <c r="M32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2104,50 +2174,53 @@
       <c r="S32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U32" s="3">
         <v>130800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E33" s="3">
         <v>31200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>40200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>34100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>47000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>36900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>36600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14400</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>5</v>
       </c>
@@ -2163,14 +2236,17 @@
       <c r="S33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
+      <c r="T33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,44 +2304,47 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E35" s="3">
         <v>31200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>40200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>34100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>47000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>36900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>36600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14400</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>5</v>
       </c>
@@ -2281,78 +2360,84 @@
       <c r="S35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
+      <c r="T35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,47 +2483,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>233200</v>
+      </c>
+      <c r="E41" s="3">
         <v>223100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>236900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>176800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>144500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>145200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>145700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>144600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>148800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>123800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>149200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>132900</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2456,8 +2543,11 @@
       <c r="U41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2515,47 +2605,50 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E43" s="3">
         <v>2400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>500</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2574,47 +2667,50 @@
       <c r="U43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>268400</v>
+      </c>
+      <c r="E44" s="3">
         <v>254300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>269000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>294900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>292100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>286400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>292600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>272500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>246500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>208300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>170600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>136100</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2633,47 +2729,50 @@
       <c r="U44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>48500</v>
+        <v>36300</v>
       </c>
       <c r="E45" s="3">
-        <v>66600</v>
+        <v>29500</v>
       </c>
       <c r="F45" s="3">
+        <v>26700</v>
+      </c>
+      <c r="G45" s="3">
         <v>47700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>51200</v>
       </c>
-      <c r="H45" s="3">
-        <v>44700</v>
-      </c>
       <c r="I45" s="3">
+        <v>27900</v>
+      </c>
+      <c r="J45" s="3">
         <v>42200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>36500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>38100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>35600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>21700</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2692,47 +2791,50 @@
       <c r="U45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>528300</v>
+        <v>539800</v>
       </c>
       <c r="E46" s="3">
-        <v>574500</v>
+        <v>509300</v>
       </c>
       <c r="F46" s="3">
+        <v>534600</v>
+      </c>
+      <c r="G46" s="3">
         <v>521000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>489800</v>
       </c>
-      <c r="H46" s="3">
-        <v>478100</v>
-      </c>
       <c r="I46" s="3">
+        <v>461200</v>
+      </c>
+      <c r="J46" s="3">
         <v>482300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>455100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>435100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>368000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>346400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>291300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2751,8 +2853,11 @@
       <c r="U46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2810,47 +2915,50 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>551200</v>
+        <v>604300</v>
       </c>
       <c r="E48" s="3">
-        <v>510500</v>
+        <v>561200</v>
       </c>
       <c r="F48" s="3">
+        <v>548600</v>
+      </c>
+      <c r="G48" s="3">
         <v>498700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>452600</v>
       </c>
-      <c r="H48" s="3">
-        <v>425600</v>
-      </c>
       <c r="I48" s="3">
+        <v>448100</v>
+      </c>
+      <c r="J48" s="3">
         <v>392800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>387900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>342600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>179600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>137000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>123600</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
@@ -2869,8 +2977,11 @@
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2907,8 +3018,8 @@
       <c r="N49" s="3">
         <v>11000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
+      <c r="O49" s="3">
+        <v>11000</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>5</v>
@@ -2928,8 +3039,11 @@
       <c r="U49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,47 +3163,50 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E52" s="3">
         <v>23700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12500</v>
       </c>
-      <c r="H52" s="3">
-        <v>17100</v>
-      </c>
       <c r="I52" s="3">
+        <v>19100</v>
+      </c>
+      <c r="J52" s="3">
         <v>21200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>23100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,47 +3287,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1114100</v>
+        <v>1176400</v>
       </c>
       <c r="E54" s="3">
-        <v>1115600</v>
+        <v>1105100</v>
       </c>
       <c r="F54" s="3">
+        <v>1113900</v>
+      </c>
+      <c r="G54" s="3">
         <v>1045300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>965900</v>
       </c>
-      <c r="H54" s="3">
-        <v>931800</v>
-      </c>
       <c r="I54" s="3">
+        <v>939400</v>
+      </c>
+      <c r="J54" s="3">
         <v>907200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>877000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>814200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>586600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>495300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>426800</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3223,8 +3349,11 @@
       <c r="U54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,47 +3399,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>62100</v>
+      </c>
+      <c r="E57" s="3">
         <v>63700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>58100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>55100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>53100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>62600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>58500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>62300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>54200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>51400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>30400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>30000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3328,8 +3459,11 @@
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3343,7 +3477,7 @@
         <v>900</v>
       </c>
       <c r="G58" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="H58" s="3">
         <v>500</v>
@@ -3355,20 +3489,20 @@
         <v>500</v>
       </c>
       <c r="K58" s="3">
+        <v>500</v>
+      </c>
+      <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O58" s="3">
         <v>200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3387,47 +3521,50 @@
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>286700</v>
+        <v>383900</v>
       </c>
       <c r="E59" s="3">
-        <v>327100</v>
+        <v>277700</v>
       </c>
       <c r="F59" s="3">
+        <v>330300</v>
+      </c>
+      <c r="G59" s="3">
         <v>288600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>293300</v>
       </c>
-      <c r="H59" s="3">
-        <v>310600</v>
-      </c>
       <c r="I59" s="3">
+        <v>312400</v>
+      </c>
+      <c r="J59" s="3">
         <v>365000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>363800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>390500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>349800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>306400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>259000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3446,47 +3583,50 @@
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>351300</v>
+        <v>446900</v>
       </c>
       <c r="E60" s="3">
-        <v>386200</v>
+        <v>342300</v>
       </c>
       <c r="F60" s="3">
+        <v>389300</v>
+      </c>
+      <c r="G60" s="3">
         <v>344600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>346800</v>
       </c>
-      <c r="H60" s="3">
-        <v>373800</v>
-      </c>
       <c r="I60" s="3">
+        <v>375600</v>
+      </c>
+      <c r="J60" s="3">
         <v>424000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>426700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>444900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>401200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>336700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>289200</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>5</v>
       </c>
@@ -3505,47 +3645,50 @@
       <c r="U60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E61" s="3">
         <v>53900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>54000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>53900</v>
-      </c>
-      <c r="G61" s="3">
-        <v>51800</v>
       </c>
       <c r="H61" s="3">
         <v>51800</v>
       </c>
       <c r="I61" s="3">
+        <v>51800</v>
+      </c>
+      <c r="J61" s="3">
         <v>51900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>52000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>50300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>47800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3564,47 +3707,50 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>390100</v>
+      </c>
+      <c r="E62" s="3">
         <v>368700</v>
       </c>
-      <c r="E62" s="3">
-        <v>366900</v>
-      </c>
       <c r="F62" s="3">
+        <v>362000</v>
+      </c>
+      <c r="G62" s="3">
         <v>359200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>322200</v>
       </c>
-      <c r="H62" s="3">
-        <v>296500</v>
-      </c>
       <c r="I62" s="3">
+        <v>302300</v>
+      </c>
+      <c r="J62" s="3">
         <v>270500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>274500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>232400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>65000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>127800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>124800</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3623,8 +3769,11 @@
       <c r="U62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,47 +3955,50 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>773900</v>
+        <v>890700</v>
       </c>
       <c r="E66" s="3">
-        <v>807100</v>
+        <v>764900</v>
       </c>
       <c r="F66" s="3">
+        <v>805400</v>
+      </c>
+      <c r="G66" s="3">
         <v>757700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>720800</v>
       </c>
-      <c r="H66" s="3">
-        <v>722100</v>
-      </c>
       <c r="I66" s="3">
+        <v>729700</v>
+      </c>
+      <c r="J66" s="3">
         <v>746400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>753100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>727600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>516800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>515100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>461700</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>5</v>
       </c>
@@ -3859,8 +4017,11 @@
       <c r="U66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,47 +4289,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>89200</v>
+      </c>
+      <c r="E72" s="3">
         <v>145300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>114100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>94300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>54200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-26900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-63900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-100500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-116600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-22700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-37000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4177,8 +4351,11 @@
       <c r="U72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,47 +4537,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>285600</v>
+      </c>
+      <c r="E76" s="3">
         <v>340200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>308500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>287600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>245100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>209700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>160800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>123900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>86500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>69800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-19800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-34900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>5</v>
       </c>
@@ -4413,8 +4599,11 @@
       <c r="U76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,108 +4661,114 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E81" s="3">
         <v>31200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>40200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>34100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>47000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>36900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>36600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14400</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>5</v>
       </c>
@@ -4589,14 +4784,17 @@
       <c r="S81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
+      <c r="T81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,53 +4816,54 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E83" s="3">
         <v>8000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>17000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
@@ -4677,8 +4876,11 @@
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,53 +5186,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>40900</v>
+        <v>36800</v>
       </c>
       <c r="E89" s="3">
-        <v>69600</v>
+        <v>24400</v>
       </c>
       <c r="F89" s="3">
-        <v>54100</v>
+        <v>86100</v>
       </c>
       <c r="G89" s="3">
-        <v>7700</v>
+        <v>50900</v>
       </c>
       <c r="H89" s="3">
-        <v>16200</v>
+        <v>10900</v>
       </c>
       <c r="I89" s="3">
-        <v>17100</v>
+        <v>12600</v>
       </c>
       <c r="J89" s="3">
+        <v>20800</v>
+      </c>
+      <c r="K89" s="3">
         <v>5900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>35200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>31800</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
         <v>150400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>5</v>
       </c>
@@ -5031,8 +5248,11 @@
       <c r="U89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,53 +5274,54 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-54700</v>
+        <v>-25900</v>
       </c>
       <c r="E91" s="3">
-        <v>-9500</v>
+        <v>-38200</v>
       </c>
       <c r="F91" s="3">
-        <v>-24300</v>
+        <v>-26000</v>
       </c>
       <c r="G91" s="3">
-        <v>-8500</v>
+        <v>-21100</v>
       </c>
       <c r="H91" s="3">
-        <v>-14400</v>
+        <v>-11700</v>
       </c>
       <c r="I91" s="3">
-        <v>-16600</v>
+        <v>-10800</v>
       </c>
       <c r="J91" s="3">
-        <v>-10200</v>
+        <v>-20200</v>
       </c>
       <c r="K91" s="3">
         <v>-10200</v>
       </c>
       <c r="L91" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="M91" s="3">
         <v>-18300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15800</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>5</v>
       </c>
@@ -5113,8 +5334,11 @@
       <c r="U91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,53 +5458,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-54700</v>
+        <v>-25900</v>
       </c>
       <c r="E94" s="3">
-        <v>-9500</v>
+        <v>-38200</v>
       </c>
       <c r="F94" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="G94" s="3">
         <v>-24300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16600</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-10200</v>
       </c>
       <c r="K94" s="3">
         <v>-10200</v>
       </c>
       <c r="L94" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="M94" s="3">
         <v>-18300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15800</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
@@ -5290,8 +5520,11 @@
       <c r="U94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,53 +5792,56 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-400</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-100</v>
       </c>
       <c r="I100" s="3">
         <v>-100</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-15900</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-98300</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
@@ -5608,8 +5854,11 @@
       <c r="U100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5667,53 +5916,56 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>59000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>29700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>25100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-30600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>16000</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
         <v>39100</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
@@ -5724,6 +5976,9 @@
         <v>5</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>ARHS</t>
   </si>
@@ -656,203 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>309800</v>
+      </c>
+      <c r="E8" s="3">
         <v>295200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>344000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>326200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>312900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>304600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>356300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>320000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>306300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>246300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>238200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>203300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>184000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>171300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>162800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>120500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>103400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>120700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>133800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>185400</v>
+      </c>
+      <c r="E9" s="3">
         <v>180100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>202800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>195400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>172800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>176300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>198300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>183700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>173200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>148600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>141300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>118500</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
@@ -874,47 +881,50 @@
       <c r="V9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>124400</v>
+      </c>
+      <c r="E10" s="3">
         <v>115100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>141200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>130800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>140100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>128300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>158000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>136300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>133100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>97700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>96900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>84800</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -936,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,19 +1101,22 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
@@ -1104,11 +1124,11 @@
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
@@ -1116,12 +1136,12 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>1500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1134,8 +1154,8 @@
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1146,8 +1166,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1155,13 +1178,13 @@
         <v>600</v>
       </c>
       <c r="E15" s="3">
+        <v>600</v>
+      </c>
+      <c r="F15" s="3">
         <v>700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>500</v>
       </c>
       <c r="H15" s="3">
         <v>500</v>
@@ -1178,8 +1201,8 @@
       <c r="L15" s="3">
         <v>500</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>5</v>
+      <c r="M15" s="3">
+        <v>500</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>5</v>
@@ -1196,8 +1219,8 @@
       <c r="R15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,47 +1255,48 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>280400</v>
+      </c>
+      <c r="E17" s="3">
         <v>276800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>303000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>302300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>258900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>259100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>291900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>272900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>256000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>223400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>242600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>186700</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1285,53 +1312,56 @@
       <c r="T17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
+      <c r="U17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E18" s="3">
         <v>18400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>41000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>23900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>54000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>45500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>64400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>47100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>50300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>22900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16600</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1347,14 +1377,17 @@
       <c r="T18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>133800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,47 +1410,48 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E20" s="3">
         <v>2900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>400</v>
       </c>
       <c r="N20" s="3">
+        <v>400</v>
+      </c>
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1433,53 +1467,56 @@
       <c r="T20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>-130800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-121600</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E21" s="3">
         <v>29900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>52300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>33800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>63300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>54300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>71700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>53600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>56500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>29100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>24500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1501,8 +1538,11 @@
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1516,28 +1556,28 @@
         <v>1400</v>
       </c>
       <c r="G22" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="H22" s="3">
         <v>1300</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>800</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1300</v>
       </c>
       <c r="L22" s="3">
         <v>1300</v>
       </c>
       <c r="M22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N22" s="3">
         <v>1400</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1300</v>
       </c>
       <c r="O22" s="3">
         <v>1300</v>
@@ -1546,64 +1586,67 @@
         <v>1300</v>
       </c>
       <c r="Q22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R22" s="3">
         <v>3200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3600</v>
-      </c>
-      <c r="T22" s="3">
-        <v>3000</v>
       </c>
       <c r="U22" s="3">
         <v>3000</v>
       </c>
       <c r="V22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="W22" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E23" s="3">
         <v>19900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>42900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>25000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>54600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>46200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>65100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>46500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>49100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>21900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14900</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1619,64 +1662,67 @@
       <c r="T23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
+      <c r="U23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E24" s="3">
         <v>4800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>18100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-11800</v>
-      </c>
-      <c r="N24" s="3">
-        <v>500</v>
       </c>
       <c r="O24" s="3">
         <v>500</v>
       </c>
       <c r="P24" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
-      </c>
-      <c r="S24" s="3">
-        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>100</v>
@@ -1685,10 +1731,13 @@
         <v>100</v>
       </c>
       <c r="V24" s="3">
+        <v>100</v>
+      </c>
+      <c r="W24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,47 +1798,50 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E26" s="3">
         <v>15100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>31200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>19700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>40200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>34100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>47000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>36900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>36600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14400</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1805,53 +1857,56 @@
       <c r="T26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
+      <c r="U26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E27" s="3">
         <v>15100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>31200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>19700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>40200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>34100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>47000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>36900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>36600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14400</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1867,14 +1922,17 @@
       <c r="T27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
+      <c r="U27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,47 +2188,50 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-400</v>
       </c>
       <c r="N32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2177,53 +2247,56 @@
       <c r="T32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>130800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E33" s="3">
         <v>15100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>31200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>19700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>40200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>34100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>47000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>36900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>36600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14400</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>5</v>
       </c>
@@ -2239,14 +2312,17 @@
       <c r="T33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
+      <c r="U33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,47 +2383,50 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E35" s="3">
         <v>15100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>31200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>19700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>40200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>34100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>47000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>36900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>36600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14400</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>5</v>
       </c>
@@ -2363,81 +2442,87 @@
       <c r="T35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
+      <c r="U35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,50 +2570,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>174200</v>
+      </c>
+      <c r="E41" s="3">
         <v>233200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>223100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>236900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>176800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>144500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>145200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>145700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>144600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>148800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>123800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>149200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>132900</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2546,8 +2633,11 @@
       <c r="V41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,50 +2698,53 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>500</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2670,50 +2763,53 @@
       <c r="V43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>273600</v>
+      </c>
+      <c r="E44" s="3">
         <v>268400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>254300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>269000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>294900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>292100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>286400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>292600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>272500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>246500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>208300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>170600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>136100</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2732,50 +2828,53 @@
       <c r="V44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E45" s="3">
         <v>36300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>29500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>26700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>47700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>51200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>27900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>42200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>36500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>35600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>26300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>21700</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2794,50 +2893,53 @@
       <c r="V45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>490500</v>
+      </c>
+      <c r="E46" s="3">
         <v>539800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>509300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>534600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>521000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>489800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>461200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>482300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>455100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>435100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>368000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>346400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>291300</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2856,8 +2958,11 @@
       <c r="V46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2918,50 +3023,53 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>658600</v>
+      </c>
+      <c r="E48" s="3">
         <v>604300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>561200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>548600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>498700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>452600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>448100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>392800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>387900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>342600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>179600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>137000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>123600</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
@@ -2980,8 +3088,11 @@
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3021,8 +3132,8 @@
       <c r="O49" s="3">
         <v>11000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
+      <c r="P49" s="3">
+        <v>11000</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>5</v>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,50 +3283,53 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E52" s="3">
         <v>21400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>28000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1000</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,50 +3413,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1177300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1176400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1105100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1113900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1045300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>965900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>939400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>907200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>877000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>814200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>586600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>495300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>426800</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3352,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,50 +3530,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E57" s="3">
         <v>62100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>63700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>58100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>55100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>53100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>62600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>58500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>62300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>54200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>51400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>30400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>30000</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3462,13 +3593,16 @@
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E58" s="3">
         <v>900</v>
@@ -3480,7 +3614,7 @@
         <v>900</v>
       </c>
       <c r="H58" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="I58" s="3">
         <v>500</v>
@@ -3492,20 +3626,20 @@
         <v>500</v>
       </c>
       <c r="L58" s="3">
+        <v>500</v>
+      </c>
+      <c r="M58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P58" s="3">
         <v>200</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3524,50 +3658,53 @@
       <c r="V58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>323200</v>
+      </c>
+      <c r="E59" s="3">
         <v>383900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>277700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>330300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>288600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>293300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>312400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>365000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>363800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>390500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>349800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>306400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>259000</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3586,50 +3723,53 @@
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>392100</v>
+      </c>
+      <c r="E60" s="3">
         <v>446900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>342300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>389300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>344600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>346800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>375600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>424000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>426700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>444900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>401200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>336700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>289200</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>5</v>
       </c>
@@ -3648,50 +3788,53 @@
       <c r="V60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E61" s="3">
         <v>53700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>53900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>54000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>53900</v>
-      </c>
-      <c r="H61" s="3">
-        <v>51800</v>
       </c>
       <c r="I61" s="3">
         <v>51800</v>
       </c>
       <c r="J61" s="3">
+        <v>51800</v>
+      </c>
+      <c r="K61" s="3">
         <v>51900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>52000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>47800</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3710,50 +3853,53 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>422200</v>
+      </c>
+      <c r="E62" s="3">
         <v>390100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>368700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>362000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>359200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>322200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>302300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>270500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>274500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>232400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>65000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>127800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>124800</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,50 +4113,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>868000</v>
+      </c>
+      <c r="E66" s="3">
         <v>890700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>764900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>805400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>757700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>720800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>729700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>746400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>753100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>727600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>516800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>515100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>461700</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4020,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,50 +4463,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E72" s="3">
         <v>89200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>145300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>114100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>94300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>54200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-26900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-63900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-100500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-116600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-22700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-37000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4354,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,50 +4723,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>309300</v>
+      </c>
+      <c r="E76" s="3">
         <v>285600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>340200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>308500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>287600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>245100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>209700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>160800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>123900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>86500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>69800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-19800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-34900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>5</v>
       </c>
@@ -4602,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,114 +4853,120 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E81" s="3">
         <v>15100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>31200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>19700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>40200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>34100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>47000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>36900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>36600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14400</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>5</v>
       </c>
@@ -4787,14 +4982,17 @@
       <c r="T81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
+      <c r="U81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,56 +5015,57 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E83" s="3">
         <v>8600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8300</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>17000</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,56 +5403,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E89" s="3">
         <v>36800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>24400</v>
       </c>
-      <c r="F89" s="3">
-        <v>86100</v>
-      </c>
       <c r="G89" s="3">
-        <v>50900</v>
+        <v>83700</v>
       </c>
       <c r="H89" s="3">
+        <v>53300</v>
+      </c>
+      <c r="I89" s="3">
         <v>10900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>20800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>35200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>31800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>150400</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
@@ -5251,8 +5468,11 @@
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,56 +5495,57 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-36200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-38200</v>
       </c>
-      <c r="F91" s="3">
-        <v>-26000</v>
-      </c>
       <c r="G91" s="3">
-        <v>-21100</v>
+        <v>-23600</v>
       </c>
       <c r="H91" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="I91" s="3">
         <v>-11700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20200</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-10200</v>
       </c>
       <c r="L91" s="3">
         <v>-10200</v>
       </c>
       <c r="M91" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-18300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15800</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3">
         <v>-13000</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>5</v>
       </c>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,56 +5688,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-36200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-25900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-38200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-24300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16600</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-10200</v>
       </c>
       <c r="L94" s="3">
         <v>-10200</v>
       </c>
       <c r="M94" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="N94" s="3">
         <v>-18300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15800</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-13000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
@@ -5523,8 +5753,11 @@
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,56 +6038,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-70300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-400</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-100</v>
       </c>
       <c r="J100" s="3">
         <v>-100</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-15900</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>-98300</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
@@ -5857,8 +6103,11 @@
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5919,56 +6168,59 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="E102" s="3">
         <v>10100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>59000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>29700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>25100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-30600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>16000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>39100</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
@@ -5979,6 +6231,9 @@
         <v>5</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="92">
   <si>
     <t>ARHS</t>
   </si>
@@ -656,213 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>319100</v>
+      </c>
+      <c r="E8" s="3">
         <v>309800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>295200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>344000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>326200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>312900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>304600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>356300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>320000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>306300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>246300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>238200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>203300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>184000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>171300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>162800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>120500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>103400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>120700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>133800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>185400</v>
+        <v>175200</v>
       </c>
       <c r="E9" s="3">
-        <v>180100</v>
+        <v>162200</v>
       </c>
       <c r="F9" s="3">
-        <v>202800</v>
+        <v>158400</v>
       </c>
       <c r="G9" s="3">
-        <v>195400</v>
+        <v>182000</v>
       </c>
       <c r="H9" s="3">
-        <v>172800</v>
+        <v>174500</v>
       </c>
       <c r="I9" s="3">
-        <v>176300</v>
+        <v>153000</v>
       </c>
       <c r="J9" s="3">
+        <v>156600</v>
+      </c>
+      <c r="K9" s="3">
         <v>198300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>183700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>173200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>148600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>141300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>118500</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
@@ -884,50 +891,53 @@
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>124400</v>
+        <v>143900</v>
       </c>
       <c r="E10" s="3">
-        <v>115100</v>
+        <v>147600</v>
       </c>
       <c r="F10" s="3">
-        <v>141200</v>
+        <v>136700</v>
       </c>
       <c r="G10" s="3">
-        <v>130800</v>
+        <v>162100</v>
       </c>
       <c r="H10" s="3">
-        <v>140100</v>
+        <v>151700</v>
       </c>
       <c r="I10" s="3">
-        <v>128300</v>
+        <v>159900</v>
       </c>
       <c r="J10" s="3">
+        <v>148000</v>
+      </c>
+      <c r="K10" s="3">
         <v>158000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>136300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>133100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>97700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>96900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>84800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -949,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1115,8 +1135,8 @@
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
@@ -1127,11 +1147,11 @@
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
@@ -1139,12 +1159,12 @@
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>1500</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1157,8 +1177,8 @@
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1169,25 +1189,28 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
         <v>600</v>
       </c>
       <c r="F15" s="3">
+        <v>600</v>
+      </c>
+      <c r="G15" s="3">
         <v>700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>500</v>
       </c>
       <c r="I15" s="3">
         <v>500</v>
@@ -1204,8 +1227,8 @@
       <c r="M15" s="3">
         <v>500</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>5</v>
+      <c r="N15" s="3">
+        <v>500</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>5</v>
@@ -1222,8 +1245,8 @@
       <c r="S15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,50 +1282,51 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>308500</v>
+      </c>
+      <c r="E17" s="3">
         <v>280400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>276800</v>
       </c>
-      <c r="F17" s="3">
-        <v>303000</v>
-      </c>
       <c r="G17" s="3">
+        <v>303400</v>
+      </c>
+      <c r="H17" s="3">
         <v>302300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>258900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>259100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>291900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>272900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>256000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>223400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>242600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>186700</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1315,56 +1342,59 @@
       <c r="U17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
+      <c r="V17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E18" s="3">
         <v>29400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18400</v>
       </c>
-      <c r="F18" s="3">
-        <v>41000</v>
-      </c>
       <c r="G18" s="3">
+        <v>40600</v>
+      </c>
+      <c r="H18" s="3">
         <v>23900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>54000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>45500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>64400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>47100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>50300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>22900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16600</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1380,14 +1410,17 @@
       <c r="U18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3">
         <v>133800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,50 +1444,51 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2100</v>
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
-        <v>2900</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>3300</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>2600</v>
+        <v>-700</v>
       </c>
       <c r="H20" s="3">
-        <v>1900</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>2000</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K20" s="3">
         <v>700</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>400</v>
       </c>
       <c r="O20" s="3">
+        <v>400</v>
+      </c>
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1470,56 +1504,59 @@
       <c r="U20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3">
         <v>-130800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-121600</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>40600</v>
+        <v>11400</v>
       </c>
       <c r="E21" s="3">
-        <v>29900</v>
+        <v>30100</v>
       </c>
       <c r="F21" s="3">
-        <v>52300</v>
+        <v>19100</v>
       </c>
       <c r="G21" s="3">
-        <v>33800</v>
+        <v>42000</v>
       </c>
       <c r="H21" s="3">
-        <v>63300</v>
+        <v>24700</v>
       </c>
       <c r="I21" s="3">
-        <v>54300</v>
+        <v>54600</v>
       </c>
       <c r="J21" s="3">
+        <v>46600</v>
+      </c>
+      <c r="K21" s="3">
         <v>71700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>53600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>56500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>29100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>24500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1541,46 +1578,49 @@
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>1400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>800</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1300</v>
       </c>
       <c r="M22" s="3">
         <v>1300</v>
       </c>
       <c r="N22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O22" s="3">
         <v>1400</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1300</v>
       </c>
       <c r="P22" s="3">
         <v>1300</v>
@@ -1589,67 +1629,70 @@
         <v>1300</v>
       </c>
       <c r="R22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S22" s="3">
         <v>3200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3600</v>
-      </c>
-      <c r="U22" s="3">
-        <v>3000</v>
       </c>
       <c r="V22" s="3">
         <v>3000</v>
       </c>
       <c r="W22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="X22" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E23" s="3">
         <v>30100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>19900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>42900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>25000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>54600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>46200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>65100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>46500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>49100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14900</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1665,67 +1708,70 @@
       <c r="U23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
+      <c r="V23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E24" s="3">
         <v>7800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>18100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-11800</v>
-      </c>
-      <c r="O24" s="3">
-        <v>500</v>
       </c>
       <c r="P24" s="3">
         <v>500</v>
       </c>
       <c r="Q24" s="3">
+        <v>500</v>
+      </c>
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>700</v>
-      </c>
-      <c r="T24" s="3">
-        <v>100</v>
       </c>
       <c r="U24" s="3">
         <v>100</v>
@@ -1734,10 +1780,13 @@
         <v>100</v>
       </c>
       <c r="W24" s="3">
+        <v>100</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,50 +1850,53 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E26" s="3">
         <v>22200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>31200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>19700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>40200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>34100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>47000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>36900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>36600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14400</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1860,56 +1912,59 @@
       <c r="U26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
+      <c r="V26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E27" s="3">
         <v>22200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>31200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>19700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>40200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>34100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>47000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>36900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>36600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14400</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1925,14 +1980,17 @@
       <c r="U27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
+      <c r="V27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,50 +2258,53 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2100</v>
+        <v>300</v>
       </c>
       <c r="E32" s="3">
-        <v>-2900</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>-3300</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>-2600</v>
+        <v>700</v>
       </c>
       <c r="H32" s="3">
-        <v>-1900</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>-2000</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
+        <v>600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-700</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-400</v>
       </c>
       <c r="O32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2250,56 +2320,59 @@
       <c r="U32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W32" s="3">
         <v>130800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E33" s="3">
         <v>22200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>31200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>19700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>40200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>34100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>47000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>36900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>36600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14400</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>5</v>
       </c>
@@ -2315,14 +2388,17 @@
       <c r="U33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
+      <c r="V33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,50 +2462,53 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E35" s="3">
         <v>22200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>31200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>19700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>40200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>34100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>47000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>36900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>36600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14400</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>5</v>
       </c>
@@ -2445,84 +2524,90 @@
       <c r="U35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
+      <c r="V35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,53 +2657,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>177700</v>
+      </c>
+      <c r="E41" s="3">
         <v>174200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>233200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>223100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>236900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>176800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>144500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>145200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>145700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>144600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>148800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>123800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>149200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>132900</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2636,16 +2723,19 @@
       <c r="W41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2701,53 +2791,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1800</v>
       </c>
-      <c r="F43" s="3">
-        <v>2400</v>
-      </c>
       <c r="G43" s="3">
+        <v>18100</v>
+      </c>
+      <c r="H43" s="3">
         <v>2000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>500</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2766,53 +2859,56 @@
       <c r="W43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>294600</v>
+      </c>
+      <c r="E44" s="3">
         <v>273600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>268400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>254300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>269000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>294900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>292100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>286400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>292600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>272500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>246500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>208300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>170600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>136100</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2831,53 +2927,56 @@
       <c r="W44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>41200</v>
+        <v>12600</v>
       </c>
       <c r="E45" s="3">
-        <v>36300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>29500</v>
+        <v>11000</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G45" s="3">
-        <v>26700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>47700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>51200</v>
-      </c>
-      <c r="J45" s="3">
+        <v>15100</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>27900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>42200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>36500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>35600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>26300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>21700</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2896,53 +2995,56 @@
       <c r="W45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>509300</v>
+      </c>
+      <c r="E46" s="3">
         <v>490500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>539800</v>
       </c>
-      <c r="F46" s="3">
-        <v>509300</v>
-      </c>
       <c r="G46" s="3">
+        <v>528300</v>
+      </c>
+      <c r="H46" s="3">
         <v>534600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>521000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>489800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>461200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>482300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>455100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>435100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>368000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>346400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>291300</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2961,31 +3063,34 @@
       <c r="W46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3026,53 +3131,56 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>671000</v>
+      </c>
+      <c r="E48" s="3">
         <v>658600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>604300</v>
       </c>
-      <c r="F48" s="3">
-        <v>561200</v>
-      </c>
       <c r="G48" s="3">
+        <v>551200</v>
+      </c>
+      <c r="H48" s="3">
         <v>548600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>498700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>452600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>448100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>392800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>387900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>342600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>179600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>137000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>123600</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3091,8 +3199,11 @@
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3135,8 +3246,8 @@
       <c r="P49" s="3">
         <v>11000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
+      <c r="Q49" s="3">
+        <v>11000</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>5</v>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,53 +3403,56 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>17300</v>
+        <v>2300</v>
       </c>
       <c r="E52" s="3">
-        <v>21400</v>
+        <v>2600</v>
       </c>
       <c r="F52" s="3">
-        <v>23700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>19700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>14600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>12500</v>
-      </c>
-      <c r="J52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
         <v>19100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>23100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,53 +3539,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1209300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1177300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1176400</v>
       </c>
-      <c r="F54" s="3">
-        <v>1105100</v>
-      </c>
       <c r="G54" s="3">
+        <v>1114100</v>
+      </c>
+      <c r="H54" s="3">
         <v>1113900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1045300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>965900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>939400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>907200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>877000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>814200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>586600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>495300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>426800</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3481,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,53 +3661,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E57" s="3">
         <v>67900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>62100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>63700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>58100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>55100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>53100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>62600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>58500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>62300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>54200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>51400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>30400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>30000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3596,31 +3727,34 @@
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1000</v>
+        <v>52700</v>
       </c>
       <c r="E58" s="3">
-        <v>900</v>
+        <v>50400</v>
       </c>
       <c r="F58" s="3">
-        <v>900</v>
+        <v>43600</v>
       </c>
       <c r="G58" s="3">
-        <v>900</v>
+        <v>46500</v>
       </c>
       <c r="H58" s="3">
-        <v>900</v>
+        <v>42200</v>
       </c>
       <c r="I58" s="3">
-        <v>500</v>
+        <v>42400</v>
       </c>
       <c r="J58" s="3">
-        <v>500</v>
+        <v>40700</v>
       </c>
       <c r="K58" s="3">
         <v>500</v>
@@ -3629,20 +3763,20 @@
         <v>500</v>
       </c>
       <c r="M58" s="3">
+        <v>500</v>
+      </c>
+      <c r="N58" s="3">
         <v>200</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3661,53 +3795,56 @@
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>323200</v>
+        <v>241900</v>
       </c>
       <c r="E59" s="3">
-        <v>383900</v>
+        <v>221800</v>
       </c>
       <c r="F59" s="3">
-        <v>277700</v>
+        <v>296200</v>
       </c>
       <c r="G59" s="3">
-        <v>330300</v>
+        <v>196300</v>
       </c>
       <c r="H59" s="3">
-        <v>288600</v>
+        <v>217000</v>
       </c>
       <c r="I59" s="3">
-        <v>293300</v>
+        <v>197900</v>
       </c>
       <c r="J59" s="3">
+        <v>202600</v>
+      </c>
+      <c r="K59" s="3">
         <v>312400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>365000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>363800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>390500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>349800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>306400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>259000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3726,53 +3863,56 @@
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>415700</v>
+      </c>
+      <c r="E60" s="3">
         <v>392100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>446900</v>
       </c>
-      <c r="F60" s="3">
-        <v>342300</v>
-      </c>
       <c r="G60" s="3">
+        <v>351300</v>
+      </c>
+      <c r="H60" s="3">
         <v>389300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>344600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>346800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>375600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>424000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>426700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>444900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>401200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>336700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>289200</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>5</v>
       </c>
@@ -3791,53 +3931,56 @@
       <c r="W60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>53600</v>
+        <v>468900</v>
       </c>
       <c r="E61" s="3">
-        <v>53700</v>
+        <v>471500</v>
       </c>
       <c r="F61" s="3">
-        <v>53900</v>
+        <v>437300</v>
       </c>
       <c r="G61" s="3">
-        <v>54000</v>
+        <v>416500</v>
       </c>
       <c r="H61" s="3">
-        <v>53900</v>
+        <v>409800</v>
       </c>
       <c r="I61" s="3">
+        <v>406800</v>
+      </c>
+      <c r="J61" s="3">
+        <v>367500</v>
+      </c>
+      <c r="K61" s="3">
         <v>51800</v>
       </c>
-      <c r="J61" s="3">
-        <v>51800</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>52000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>50600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>47800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3856,53 +3999,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>422200</v>
+        <v>4100</v>
       </c>
       <c r="E62" s="3">
-        <v>390100</v>
+        <v>4400</v>
       </c>
       <c r="F62" s="3">
-        <v>368700</v>
+        <v>6400</v>
       </c>
       <c r="G62" s="3">
-        <v>362000</v>
+        <v>6100</v>
       </c>
       <c r="H62" s="3">
-        <v>359200</v>
+        <v>6200</v>
       </c>
       <c r="I62" s="3">
-        <v>322200</v>
+        <v>6300</v>
       </c>
       <c r="J62" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K62" s="3">
         <v>302300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>270500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>274500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>232400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>65000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>127800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>124800</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,53 +4271,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>888700</v>
+      </c>
+      <c r="E66" s="3">
         <v>868000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>890700</v>
       </c>
-      <c r="F66" s="3">
-        <v>764900</v>
-      </c>
       <c r="G66" s="3">
+        <v>773900</v>
+      </c>
+      <c r="H66" s="3">
         <v>805400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>757700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>720800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>729700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>746400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>753100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>727600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>516800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>515100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>461700</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,53 +4637,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>121600</v>
+      </c>
+      <c r="E72" s="3">
         <v>111500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>89200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>145300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>114100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>94300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>54200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-26900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-63900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-100500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-116600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-22700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,53 +4909,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>320600</v>
+      </c>
+      <c r="E76" s="3">
         <v>309300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>285600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>340200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>308500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>287600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>245100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>209700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>160800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>123900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>86500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>69800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-19800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-34900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>5</v>
       </c>
@@ -4791,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,120 +5045,126 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E81" s="3">
         <v>22200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>31200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>19700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>40200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>34100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>47000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>36900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>36600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14400</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>5</v>
       </c>
@@ -4985,14 +5180,17 @@
       <c r="U81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
+      <c r="V81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,59 +5214,60 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>9100</v>
+        <v>16000</v>
       </c>
       <c r="E83" s="3">
-        <v>8600</v>
+        <v>15900</v>
       </c>
       <c r="F83" s="3">
-        <v>8000</v>
+        <v>14300</v>
       </c>
       <c r="G83" s="3">
-        <v>7300</v>
+        <v>13700</v>
       </c>
       <c r="H83" s="3">
-        <v>7400</v>
+        <v>13800</v>
       </c>
       <c r="I83" s="3">
+        <v>13600</v>
+      </c>
+      <c r="J83" s="3">
+        <v>12900</v>
+      </c>
+      <c r="K83" s="3">
+        <v>6600</v>
+      </c>
+      <c r="L83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="M83" s="3">
+        <v>6100</v>
+      </c>
+      <c r="N83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="O83" s="3">
         <v>6700</v>
       </c>
-      <c r="J83" s="3">
-        <v>6600</v>
-      </c>
-      <c r="K83" s="3">
-        <v>6300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>6100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>5900</v>
-      </c>
-      <c r="N83" s="3">
-        <v>6700</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8300</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3">
         <v>17000</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,59 +5620,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E89" s="3">
         <v>47500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>36800</v>
       </c>
-      <c r="F89" s="3">
-        <v>24400</v>
-      </c>
       <c r="G89" s="3">
+        <v>26500</v>
+      </c>
+      <c r="H89" s="3">
         <v>83700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>53300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>20800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>35200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>31800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
         <v>150400</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
@@ -5471,8 +5688,11 @@
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,59 +5716,60 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-36200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25900</v>
       </c>
-      <c r="F91" s="3">
-        <v>-38200</v>
-      </c>
       <c r="G91" s="3">
+        <v>-40300</v>
+      </c>
+      <c r="H91" s="3">
         <v>-23600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-23500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20200</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-10200</v>
       </c>
       <c r="M91" s="3">
         <v>-10200</v>
       </c>
       <c r="N91" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="O91" s="3">
         <v>-18300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15800</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S91" s="3">
         <v>-13000</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,59 +5918,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-36200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-25900</v>
       </c>
-      <c r="F94" s="3">
-        <v>-38200</v>
-      </c>
       <c r="G94" s="3">
-        <v>-26000</v>
+        <v>-40300</v>
       </c>
       <c r="H94" s="3">
-        <v>-24300</v>
+        <v>-23600</v>
       </c>
       <c r="I94" s="3">
-        <v>-8200</v>
+        <v>-23500</v>
       </c>
       <c r="J94" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-14400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16600</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-10200</v>
       </c>
       <c r="M94" s="3">
         <v>-10200</v>
       </c>
       <c r="N94" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="O94" s="3">
         <v>-18300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15800</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3">
         <v>-13000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
@@ -5756,8 +5986,11 @@
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,31 +6014,32 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>70100</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,59 +6284,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-70300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-400</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-100</v>
       </c>
       <c r="K100" s="3">
         <v>-100</v>
       </c>
       <c r="L100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-15900</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
         <v>-98300</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
@@ -6106,31 +6352,34 @@
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6171,59 +6420,62 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-59000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>59000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>29700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>25100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-30600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>16000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
         <v>39100</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
@@ -6234,6 +6486,9 @@
         <v>5</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="92">
   <si>
     <t>ARHS</t>
   </si>
@@ -656,223 +656,229 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>347000</v>
+      </c>
+      <c r="E8" s="3">
         <v>319100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>309800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>295200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>344000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>326200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>312900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>304600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>356300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>320000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>306300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>246300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>238200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>203300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>184000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>171300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>162800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>120500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>103400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>120700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>133800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>189500</v>
+      </c>
+      <c r="E9" s="3">
         <v>175200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>162200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>158400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>182000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>174500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>153000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>156600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>198300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>183700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>173200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>148600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>141300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>118500</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -894,53 +900,56 @@
       <c r="X9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>157500</v>
+      </c>
+      <c r="E10" s="3">
         <v>143900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>147600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>136700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>162100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>151700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>159900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>148000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>158000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>136300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>133100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>97700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>96900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>84800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -962,8 +971,11 @@
       <c r="X10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1000,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1069,11 @@
       <c r="X12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,13 +1140,16 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>-1200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1150,11 +1169,11 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
@@ -1162,12 +1181,12 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>1500</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1180,8 +1199,8 @@
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1192,28 +1211,31 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>800</v>
+      </c>
+      <c r="E15" s="3">
         <v>500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>600</v>
       </c>
       <c r="F15" s="3">
         <v>600</v>
       </c>
       <c r="G15" s="3">
+        <v>600</v>
+      </c>
+      <c r="H15" s="3">
         <v>700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>500</v>
       </c>
       <c r="J15" s="3">
         <v>500</v>
@@ -1230,8 +1252,8 @@
       <c r="N15" s="3">
         <v>500</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>5</v>
+      <c r="O15" s="3">
+        <v>500</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>5</v>
@@ -1248,8 +1270,8 @@
       <c r="T15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1260,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,53 +1308,54 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>319600</v>
+      </c>
+      <c r="E17" s="3">
         <v>308500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>280400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>276800</v>
       </c>
-      <c r="G17" s="3">
-        <v>303400</v>
-      </c>
       <c r="H17" s="3">
+        <v>303000</v>
+      </c>
+      <c r="I17" s="3">
         <v>302300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>258900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>259100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>291900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>272900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>256000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>223400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>242600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>186700</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1345,59 +1371,62 @@
       <c r="V17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
+      <c r="W17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E18" s="3">
         <v>10700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>29400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18400</v>
       </c>
-      <c r="G18" s="3">
-        <v>40600</v>
-      </c>
       <c r="H18" s="3">
+        <v>41000</v>
+      </c>
+      <c r="I18" s="3">
         <v>23900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>54000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>45500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>64400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>47100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>50300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>22900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16600</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1413,14 +1442,17 @@
       <c r="V18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>133800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,8 +1477,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1454,44 +1487,44 @@
         <v>-300</v>
       </c>
       <c r="E20" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="F20" s="3">
         <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>-700</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="I20" s="3">
         <v>-100</v>
       </c>
       <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>400</v>
       </c>
       <c r="P20" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1507,59 +1540,62 @@
       <c r="V20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>-130800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-121600</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E21" s="3">
         <v>11400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>30100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>42000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>24700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>54600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>46600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>71700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>53600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>56500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>29100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>24500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1581,13 +1617,16 @@
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
+      <c r="D22" s="3">
+        <v>5400</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>5</v>
@@ -1598,8 +1637,8 @@
       <c r="G22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
+      <c r="H22" s="3">
+        <v>5400</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>5</v>
@@ -1607,23 +1646,23 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1300</v>
       </c>
       <c r="N22" s="3">
         <v>1300</v>
       </c>
       <c r="O22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P22" s="3">
         <v>1400</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1300</v>
       </c>
       <c r="Q22" s="3">
         <v>1300</v>
@@ -1632,70 +1671,73 @@
         <v>1300</v>
       </c>
       <c r="S22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T22" s="3">
         <v>3200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3600</v>
-      </c>
-      <c r="V22" s="3">
-        <v>3000</v>
       </c>
       <c r="W22" s="3">
         <v>3000</v>
       </c>
       <c r="X22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E23" s="3">
         <v>11500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>30100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>19900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>42900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>25000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>54600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>46200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>65100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>46500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>49100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14900</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1711,70 +1753,73 @@
       <c r="V23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
+      <c r="W23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>18100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-11800</v>
-      </c>
-      <c r="P24" s="3">
-        <v>500</v>
       </c>
       <c r="Q24" s="3">
         <v>500</v>
       </c>
       <c r="R24" s="3">
+        <v>500</v>
+      </c>
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
-      </c>
-      <c r="U24" s="3">
-        <v>100</v>
       </c>
       <c r="V24" s="3">
         <v>100</v>
@@ -1783,10 +1828,13 @@
         <v>100</v>
       </c>
       <c r="X24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,53 +1901,56 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E26" s="3">
         <v>9900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>31200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>40200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>34100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>47000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>36900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>36600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14400</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1915,59 +1966,62 @@
       <c r="V26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
+      <c r="W26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E27" s="3">
         <v>9900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>22200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>31200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>40200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>34100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>47000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>36900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>36600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>14400</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1983,14 +2037,17 @@
       <c r="V27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
+      <c r="W27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,8 +2327,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2270,44 +2339,44 @@
         <v>300</v>
       </c>
       <c r="E32" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F32" s="3">
         <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I32" s="3">
         <v>100</v>
       </c>
       <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>-400</v>
       </c>
       <c r="P32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2323,59 +2392,62 @@
       <c r="V32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>130800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E33" s="3">
         <v>9900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>31200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>40200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>34100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>47000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>36900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>36600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>14400</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>5</v>
       </c>
@@ -2391,14 +2463,17 @@
       <c r="V33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
+      <c r="W33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,53 +2540,56 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E35" s="3">
         <v>9900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>31200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>40200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>34100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>47000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>36900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>36600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>14400</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>5</v>
       </c>
@@ -2527,87 +2605,93 @@
       <c r="V35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
+      <c r="W35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,56 +2743,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>197500</v>
+      </c>
+      <c r="E41" s="3">
         <v>177700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>174200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>233200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>223100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>236900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>176800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>144500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>145200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>145700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>144600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>148800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>123800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>149200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>132900</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2726,25 +2812,28 @@
       <c r="X41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E42" s="3">
         <v>5500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8400</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -2794,56 +2883,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1800</v>
       </c>
-      <c r="G43" s="3">
-        <v>18100</v>
-      </c>
       <c r="H43" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I43" s="3">
         <v>2000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>500</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2862,56 +2954,59 @@
       <c r="X43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>297000</v>
+      </c>
+      <c r="E44" s="3">
         <v>294600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>273600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>268400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>254300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>269000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>294900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>292100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>286400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>292600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>272500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>246500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>208300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>170600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>136100</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2930,25 +3025,28 @@
       <c r="X44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E45" s="3">
         <v>12600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11000</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G45" s="3">
-        <v>15100</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
+        <v>11900</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>5</v>
@@ -2956,30 +3054,30 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>27900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>42200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>36500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>38100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>35600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>26300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>21700</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2998,56 +3096,59 @@
       <c r="X45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E46" s="3">
         <v>509300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>490500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>539800</v>
       </c>
-      <c r="G46" s="3">
-        <v>528300</v>
-      </c>
       <c r="H46" s="3">
+        <v>509300</v>
+      </c>
+      <c r="I46" s="3">
         <v>534600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>521000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>489800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>461200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>482300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>455100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>435100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>368000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>346400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>291300</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3066,8 +3167,11 @@
       <c r="X46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3092,8 +3196,8 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3134,56 +3238,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>640900</v>
+      </c>
+      <c r="E48" s="3">
         <v>671000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>658600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>604300</v>
       </c>
-      <c r="G48" s="3">
-        <v>551200</v>
-      </c>
       <c r="H48" s="3">
+        <v>561200</v>
+      </c>
+      <c r="I48" s="3">
         <v>548600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>498700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>452600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>448100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>392800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>387900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>342600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>179600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>137000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>123600</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3202,8 +3309,11 @@
       <c r="X48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3249,8 +3359,8 @@
       <c r="Q49" s="3">
         <v>11000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
+      <c r="R49" s="3">
+        <v>11000</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>5</v>
@@ -3270,8 +3380,11 @@
       <c r="X49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,25 +3522,28 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E52" s="3">
         <v>2300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2000</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
+      <c r="H52" s="3">
+        <v>4100</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>5</v>
@@ -3432,30 +3551,30 @@
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3">
         <v>19100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>28000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1000</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3474,8 +3593,11 @@
       <c r="X52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,56 +3664,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1206300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1209300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1177300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1176400</v>
       </c>
-      <c r="G54" s="3">
-        <v>1114100</v>
-      </c>
       <c r="H54" s="3">
+        <v>1105100</v>
+      </c>
+      <c r="I54" s="3">
         <v>1113900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1045300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>965900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>939400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>907200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>877000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>814200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>586600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>495300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>426800</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3610,8 +3735,11 @@
       <c r="X54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,56 +3791,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E57" s="3">
         <v>73600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>67900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>62100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>63700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>58100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>55100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>53100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>62600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>58500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>62300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>54200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>51400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>30400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>30000</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3730,34 +3860,37 @@
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E58" s="3">
         <v>52700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>50400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>43600</v>
       </c>
-      <c r="G58" s="3">
-        <v>46500</v>
-      </c>
       <c r="H58" s="3">
+        <v>34000</v>
+      </c>
+      <c r="I58" s="3">
         <v>42200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>42400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>40700</v>
-      </c>
-      <c r="K58" s="3">
-        <v>500</v>
       </c>
       <c r="L58" s="3">
         <v>500</v>
@@ -3766,20 +3899,20 @@
         <v>500</v>
       </c>
       <c r="N58" s="3">
+        <v>500</v>
+      </c>
+      <c r="O58" s="3">
         <v>200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3798,56 +3931,59 @@
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>247800</v>
+      </c>
+      <c r="E59" s="3">
         <v>241900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>221800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>296200</v>
       </c>
-      <c r="G59" s="3">
-        <v>196300</v>
-      </c>
       <c r="H59" s="3">
+        <v>197500</v>
+      </c>
+      <c r="I59" s="3">
         <v>217000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>197900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>202600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>312400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>365000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>363800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>390500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>349800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>306400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>259000</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3866,56 +4002,59 @@
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>402500</v>
+      </c>
+      <c r="E60" s="3">
         <v>415700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>392100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>446900</v>
       </c>
-      <c r="G60" s="3">
-        <v>351300</v>
-      </c>
       <c r="H60" s="3">
+        <v>342300</v>
+      </c>
+      <c r="I60" s="3">
         <v>389300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>344600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>346800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>375600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>424000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>426700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>444900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>401200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>336700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>289200</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
@@ -3934,56 +4073,59 @@
       <c r="X60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>456200</v>
+      </c>
+      <c r="E61" s="3">
         <v>468900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>471500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>437300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>416500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>409800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>406800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>367500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>52000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>50500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>50600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>47800</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4002,56 +4144,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E62" s="3">
         <v>4100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>302300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>270500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>274500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>232400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>65000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>127800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>124800</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
@@ -4070,8 +4215,11 @@
       <c r="X62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,56 +4428,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>862600</v>
+      </c>
+      <c r="E66" s="3">
         <v>888700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>868000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>890700</v>
       </c>
-      <c r="G66" s="3">
-        <v>773900</v>
-      </c>
       <c r="H66" s="3">
+        <v>764900</v>
+      </c>
+      <c r="I66" s="3">
         <v>805400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>757700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>720800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>729700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>746400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>753100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>727600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>516800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>515100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>461700</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4342,8 +4499,11 @@
       <c r="X66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,56 +4810,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>142900</v>
+      </c>
+      <c r="E72" s="3">
         <v>121600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>111500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>89200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>145300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>114100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>94300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>54200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-26900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-63900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-100500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-116600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-22700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-37000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4708,8 +4881,11 @@
       <c r="X72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,56 +5094,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>343700</v>
+      </c>
+      <c r="E76" s="3">
         <v>320600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>309300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>285600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>340200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>308500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>287600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>245100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>209700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>160800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>123900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>86500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>69800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-34900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
@@ -4980,8 +5165,11 @@
       <c r="X76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,126 +5236,132 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E81" s="3">
         <v>9900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>31200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>40200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>34100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>47000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>36900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>36600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>14400</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>5</v>
       </c>
@@ -5183,14 +5377,17 @@
       <c r="V81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
+      <c r="W81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,62 +5412,63 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E83" s="3">
         <v>16000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8300</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>17000</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5283,8 +5481,11 @@
       <c r="X83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,62 +5836,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E89" s="3">
         <v>31100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>47500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>36800</v>
       </c>
-      <c r="G89" s="3">
-        <v>26500</v>
-      </c>
       <c r="H89" s="3">
+        <v>20800</v>
+      </c>
+      <c r="I89" s="3">
         <v>83700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>53300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>20800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>35200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>31800</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>150400</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>5</v>
       </c>
@@ -5691,8 +5907,11 @@
       <c r="X89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,62 +5936,63 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-26500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-36200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25900</v>
       </c>
-      <c r="G91" s="3">
-        <v>-40300</v>
-      </c>
       <c r="H91" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="I91" s="3">
         <v>-23600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-23500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20200</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-10200</v>
       </c>
       <c r="N91" s="3">
         <v>-10200</v>
       </c>
       <c r="O91" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="P91" s="3">
         <v>-18300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15800</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T91" s="3">
         <v>-13000</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>5</v>
       </c>
@@ -5785,8 +6005,11 @@
       <c r="X91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,62 +6147,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-26500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-36200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-25900</v>
       </c>
-      <c r="G94" s="3">
-        <v>-40300</v>
-      </c>
       <c r="H94" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="I94" s="3">
         <v>-23600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16600</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-10200</v>
       </c>
       <c r="N94" s="3">
         <v>-10200</v>
       </c>
       <c r="O94" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="P94" s="3">
         <v>-18300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-15800</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-13000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>5</v>
       </c>
@@ -5989,8 +6218,11 @@
       <c r="X94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6024,11 +6257,11 @@
         <v>100</v>
       </c>
       <c r="E96" s="3">
+        <v>100</v>
+      </c>
+      <c r="F96" s="3">
         <v>70100</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>5</v>
       </c>
@@ -6041,8 +6274,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6083,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,62 +6529,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-70300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-400</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-100</v>
       </c>
       <c r="L100" s="3">
         <v>-100</v>
       </c>
       <c r="M100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-15900</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-98300</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>5</v>
       </c>
@@ -6355,8 +6600,11 @@
       <c r="X100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6381,8 +6629,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6423,62 +6671,65 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-59000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>59000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>29700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>25100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-30600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>16000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>39100</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
@@ -6489,6 +6740,9 @@
         <v>5</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
   <si>
     <t>ARHS</t>
   </si>
@@ -656,232 +656,239 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>311400</v>
+      </c>
+      <c r="E8" s="3">
         <v>347000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>319100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>309800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>295200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>344000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>326200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>312900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>304600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>356300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>320000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>306300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>246300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>238200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>203300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>184000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>171300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>162800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>120500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>103400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>120700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>133800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>195800</v>
+      </c>
+      <c r="E9" s="3">
         <v>189500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>175200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>162200</v>
       </c>
-      <c r="G9" s="3">
-        <v>158400</v>
-      </c>
       <c r="H9" s="3">
+        <v>180100</v>
+      </c>
+      <c r="I9" s="3">
         <v>182000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>174500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>153000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>156600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>198300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>183700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>173200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>148600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>141300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>118500</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>5</v>
       </c>
@@ -903,56 +910,59 @@
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E10" s="3">
         <v>157500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>143900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>147600</v>
       </c>
-      <c r="G10" s="3">
-        <v>136700</v>
-      </c>
       <c r="H10" s="3">
+        <v>115100</v>
+      </c>
+      <c r="I10" s="3">
         <v>162100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>151700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>159900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>148000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>158000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>136300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>133100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>97700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>96900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>84800</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>5</v>
       </c>
@@ -974,8 +984,11 @@
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1072,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,17 +1160,20 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1172,11 +1192,11 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
@@ -1184,12 +1204,12 @@
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1202,8 +1222,8 @@
       <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1214,31 +1234,34 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>600</v>
       </c>
       <c r="G15" s="3">
         <v>600</v>
       </c>
       <c r="H15" s="3">
+        <v>600</v>
+      </c>
+      <c r="I15" s="3">
         <v>700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>500</v>
@@ -1255,8 +1278,8 @@
       <c r="O15" s="3">
         <v>500</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>5</v>
+      <c r="P15" s="3">
+        <v>500</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>5</v>
@@ -1273,8 +1296,8 @@
       <c r="U15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1285,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,56 +1335,57 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>305800</v>
+      </c>
+      <c r="E17" s="3">
         <v>319600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>308500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>280400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>276800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>303000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>302300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>258900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>259100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>291900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>272900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>256000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>223400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>242600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>186700</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1374,62 +1401,65 @@
       <c r="W17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X17" s="3">
-        <v>0</v>
+      <c r="X17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E18" s="3">
         <v>27400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>29400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>41000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>23900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>54000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>45500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>64400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>47100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>50300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>22900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>16600</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1445,14 +1475,17 @@
       <c r="W18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3">
         <v>133800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,56 +1511,57 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>-300</v>
       </c>
       <c r="F20" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="G20" s="3">
         <v>-100</v>
       </c>
       <c r="H20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I20" s="3">
         <v>-300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-100</v>
       </c>
       <c r="J20" s="3">
         <v>-100</v>
       </c>
       <c r="K20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>700</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>400</v>
       </c>
       <c r="Q20" s="3">
+        <v>400</v>
+      </c>
+      <c r="R20" s="3">
         <v>-400</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1543,62 +1577,65 @@
       <c r="W20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-130800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-121600</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E21" s="3">
         <v>28500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>30100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>19100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>42000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>24700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>54600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>46600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>71700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>53600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>56500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>29100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>24500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1620,52 +1657,55 @@
       <c r="Y21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3">
         <v>5400</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3">
         <v>5400</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>800</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1300</v>
       </c>
       <c r="O22" s="3">
         <v>1300</v>
       </c>
       <c r="P22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1300</v>
       </c>
       <c r="R22" s="3">
         <v>1300</v>
@@ -1674,73 +1714,76 @@
         <v>1300</v>
       </c>
       <c r="T22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U22" s="3">
         <v>3200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3600</v>
-      </c>
-      <c r="W22" s="3">
-        <v>3000</v>
       </c>
       <c r="X22" s="3">
         <v>3000</v>
       </c>
       <c r="Y22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E23" s="3">
         <v>29500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>30100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>19900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>42900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>25000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>54600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>46200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>65100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>46500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>49100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>21900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>14900</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1756,73 +1799,76 @@
       <c r="W23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
+      <c r="X23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>8200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>18100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-11800</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>500</v>
       </c>
       <c r="R24" s="3">
         <v>500</v>
       </c>
       <c r="S24" s="3">
+        <v>500</v>
+      </c>
+      <c r="T24" s="3">
         <v>700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>700</v>
-      </c>
-      <c r="V24" s="3">
-        <v>100</v>
       </c>
       <c r="W24" s="3">
         <v>100</v>
@@ -1831,10 +1877,13 @@
         <v>100</v>
       </c>
       <c r="Y24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,56 +1953,59 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E26" s="3">
         <v>21300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>22200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>31200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>40200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>34100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>47000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>36900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>36600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>14400</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1969,62 +2021,65 @@
       <c r="W26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
+      <c r="X26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E27" s="3">
         <v>21300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>22200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>31200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>40200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>34100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>47000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>36900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>36600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>14400</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>5</v>
       </c>
@@ -2040,14 +2095,17 @@
       <c r="W27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
+      <c r="X27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,56 +2397,59 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>300</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G32" s="3">
         <v>100</v>
       </c>
       <c r="H32" s="3">
+        <v>100</v>
+      </c>
+      <c r="I32" s="3">
         <v>300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>100</v>
       </c>
       <c r="J32" s="3">
         <v>100</v>
       </c>
       <c r="K32" s="3">
+        <v>100</v>
+      </c>
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-700</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-400</v>
       </c>
       <c r="Q32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R32" s="3">
         <v>400</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2395,62 +2465,65 @@
       <c r="W32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="3">
         <v>130800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E33" s="3">
         <v>21300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>22200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>31200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>40200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>34100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>47000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>36900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>36600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>14400</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>5</v>
       </c>
@@ -2466,14 +2539,17 @@
       <c r="W33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
+      <c r="X33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,56 +2619,59 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E35" s="3">
         <v>21300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>22200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>31200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>40200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>34100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>47000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>36900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>36600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>14400</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>5</v>
       </c>
@@ -2608,90 +2687,96 @@
       <c r="W35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
+      <c r="X35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,59 +2830,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>214400</v>
+      </c>
+      <c r="E41" s="3">
         <v>197500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>177700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>174200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>233200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>223100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>236900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>176800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>144500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>145200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>145700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>144600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>148800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>123800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>149200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>132900</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2815,29 +2902,32 @@
       <c r="Y41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>4900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8400</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>4500</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -2886,59 +2976,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>500</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2957,59 +3050,62 @@
       <c r="Y43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>301400</v>
+      </c>
+      <c r="E44" s="3">
         <v>297000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>294600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>273600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>268400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>254300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>269000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>294900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>292100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>286400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>292600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>272500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>246500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>208300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>170600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>136100</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3028,59 +3124,62 @@
       <c r="Y44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>13600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11000</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>11900</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>27900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>42200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>36500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>26300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>21700</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3099,59 +3198,62 @@
       <c r="Y45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>552800</v>
+      </c>
+      <c r="E46" s="3">
         <v>531000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>509300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>490500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>539800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>509300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>534600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>521000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>489800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>461200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>482300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>455100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>435100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>368000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>346400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>291300</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3170,8 +3272,11 @@
       <c r="Y46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3199,8 +3304,8 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3241,59 +3346,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>677800</v>
+      </c>
+      <c r="E48" s="3">
         <v>640900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>671000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>658600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>604300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>561200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>548600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>498700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>452600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>448100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>392800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>387900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>342600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>179600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>137000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>123600</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3312,8 +3420,11 @@
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3362,8 +3473,8 @@
       <c r="R49" s="3">
         <v>11000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
+      <c r="S49" s="3">
+        <v>11000</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>5</v>
@@ -3383,8 +3494,11 @@
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,59 +3642,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3">
         <v>19100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>23100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>28000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3596,8 +3716,11 @@
       <c r="Y52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,59 +3790,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1264900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1206300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1209300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1177300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1176400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1105100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1113900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1045300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>965900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>939400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>907200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>877000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>814200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>586600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>495300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>426800</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3738,8 +3864,11 @@
       <c r="Y54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,59 +3922,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E57" s="3">
         <v>68600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>73600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>67900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>62100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>63700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>58100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>55100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>53100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>62600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>58500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>62300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>54200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>51400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>30400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>30000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3863,37 +3994,40 @@
       <c r="Y57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E58" s="3">
         <v>43300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>52700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>50400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>43600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>34000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>42200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>42400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>40700</v>
-      </c>
-      <c r="L58" s="3">
-        <v>500</v>
       </c>
       <c r="M58" s="3">
         <v>500</v>
@@ -3902,20 +4036,20 @@
         <v>500</v>
       </c>
       <c r="O58" s="3">
+        <v>500</v>
+      </c>
+      <c r="P58" s="3">
         <v>200</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3934,59 +4068,62 @@
       <c r="Y58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>286200</v>
+      </c>
+      <c r="E59" s="3">
         <v>247800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>241900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>221800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>296200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>197500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>217000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>197900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>202600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>312400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>365000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>363800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>390500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>349800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>306400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>259000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4005,59 +4142,62 @@
       <c r="Y59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>437300</v>
+      </c>
+      <c r="E60" s="3">
         <v>402500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>415700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>392100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>446900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>342300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>389300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>344600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>346800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>375600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>424000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>426700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>444900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>401200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>336700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>289200</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>5</v>
       </c>
@@ -4076,59 +4216,62 @@
       <c r="Y60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>475400</v>
+      </c>
+      <c r="E61" s="3">
         <v>456200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>468900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>471500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>437300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>416500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>409800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>406800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>367500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>52000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>50300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>50500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>50600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>47800</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4147,59 +4290,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E62" s="3">
         <v>3900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>302300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>270500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>274500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>232400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>65000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>127800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>124800</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>5</v>
       </c>
@@ -4218,8 +4364,11 @@
       <c r="Y62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,59 +4586,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>916100</v>
+      </c>
+      <c r="E66" s="3">
         <v>862600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>888700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>868000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>890700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>764900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>805400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>757700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>720800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>729700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>746400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>753100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>727600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>516800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>515100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>461700</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4502,8 +4660,11 @@
       <c r="Y66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4742,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,59 +4984,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>147800</v>
+      </c>
+      <c r="E72" s="3">
         <v>142900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>121600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>111500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>89200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>145300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>114100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>94300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>54200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-26900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-63900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-100500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-116600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-22700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-37000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4884,8 +5058,11 @@
       <c r="Y72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,59 +5280,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>348800</v>
+      </c>
+      <c r="E76" s="3">
         <v>343700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>320600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>309300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>285600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>340200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>308500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>287600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>245100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>209700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>160800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>123900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>86500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>69800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-19800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-34900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>5</v>
       </c>
@@ -5168,8 +5354,11 @@
       <c r="Y76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,132 +5428,138 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E81" s="3">
         <v>21300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>22200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>31200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>40200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>34100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>47000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>36900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>36600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>14400</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>5</v>
       </c>
@@ -5380,14 +5575,17 @@
       <c r="W81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
+      <c r="X81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,65 +5611,66 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E83" s="3">
         <v>16600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8300</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3">
         <v>17000</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5484,8 +5683,11 @@
       <c r="Y83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,65 +6053,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E89" s="3">
         <v>31700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>31100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>47500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>36800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>20800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>83700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>53300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>20800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>35200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>31800</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
         <v>150400</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
@@ -5910,8 +6127,11 @@
       <c r="Y89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,65 +6157,66 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-26500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-36200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-25900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-34600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-23600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-23500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20200</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-10200</v>
       </c>
       <c r="O91" s="3">
         <v>-10200</v>
       </c>
       <c r="P91" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15800</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U91" s="3">
         <v>-13000</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
@@ -6008,8 +6229,11 @@
       <c r="Y91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,65 +6377,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-26500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-36200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-34600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-23500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16600</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-10200</v>
       </c>
       <c r="O94" s="3">
         <v>-10200</v>
       </c>
       <c r="P94" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15800</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
         <v>-13000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
@@ -6221,8 +6451,11 @@
       <c r="Y94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,23 +6481,24 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E96" s="3">
         <v>100</v>
       </c>
       <c r="F96" s="3">
+        <v>100</v>
+      </c>
+      <c r="G96" s="3">
         <v>70100</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>5</v>
       </c>
@@ -6277,8 +6511,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,65 +6775,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-70300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-400</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-100</v>
       </c>
       <c r="M100" s="3">
         <v>-100</v>
       </c>
       <c r="N100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
         <v>-98300</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
@@ -6603,8 +6849,11 @@
       <c r="Y100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6632,8 +6881,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6674,65 +6923,68 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E102" s="3">
         <v>20000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-59000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>59000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>29700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>16000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
         <v>39100</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
@@ -6743,6 +6995,9 @@
         <v>5</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
   <si>
     <t>ARHS</t>
   </si>
@@ -656,242 +656,249 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>358400</v>
+      </c>
+      <c r="E8" s="3">
         <v>311400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>347000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>319100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>309800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>295200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>344000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>326200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>312900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>304600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>356300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>320000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>306300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>246300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>238200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>203300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>184000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>171300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>162800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>120500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>103400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>120700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>133800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>210200</v>
+      </c>
+      <c r="E9" s="3">
         <v>195800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>189500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>175200</v>
       </c>
-      <c r="G9" s="3">
-        <v>162200</v>
-      </c>
       <c r="H9" s="3">
+        <v>185400</v>
+      </c>
+      <c r="I9" s="3">
         <v>180100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>182000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>174500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>153000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>156600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>198300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>183700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>173200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>148600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>141300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>118500</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>5</v>
       </c>
@@ -913,59 +920,62 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>148200</v>
+      </c>
+      <c r="E10" s="3">
         <v>115600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>157500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>143900</v>
       </c>
-      <c r="G10" s="3">
-        <v>147600</v>
-      </c>
       <c r="H10" s="3">
+        <v>124400</v>
+      </c>
+      <c r="I10" s="3">
         <v>115100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>162100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>151700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>159900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>148000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>158000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>136300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>133100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>97700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>96900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>84800</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>5</v>
       </c>
@@ -987,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,20 +1180,23 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1195,11 +1215,11 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
@@ -1207,12 +1227,12 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>1500</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1225,8 +1245,8 @@
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1237,34 +1257,37 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>500</v>
+      </c>
+      <c r="E15" s="3">
         <v>600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>500</v>
-      </c>
-      <c r="G15" s="3">
-        <v>600</v>
       </c>
       <c r="H15" s="3">
         <v>600</v>
       </c>
       <c r="I15" s="3">
+        <v>600</v>
+      </c>
+      <c r="J15" s="3">
         <v>700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>500</v>
       </c>
       <c r="L15" s="3">
         <v>500</v>
@@ -1281,8 +1304,8 @@
       <c r="P15" s="3">
         <v>500</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>5</v>
+      <c r="Q15" s="3">
+        <v>500</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>5</v>
@@ -1299,8 +1322,8 @@
       <c r="V15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,59 +1362,60 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>311700</v>
+      </c>
+      <c r="E17" s="3">
         <v>305800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>319600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>308500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>280400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>276800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>303000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>302300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>258900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>259100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>291900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>272900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>256000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>223400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>242600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>186700</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1404,65 +1431,68 @@
       <c r="X17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y17" s="3">
-        <v>0</v>
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E18" s="3">
         <v>5500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>27400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>29400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>41000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>23900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>54000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>45500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>64400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>47100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>50300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>22900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>16600</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1478,14 +1508,17 @@
       <c r="X18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>133800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,59 +1545,60 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-300</v>
       </c>
       <c r="F20" s="3">
         <v>-300</v>
       </c>
       <c r="G20" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="H20" s="3">
         <v>-100</v>
       </c>
       <c r="I20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3">
         <v>-300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-100</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
       </c>
       <c r="L20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M20" s="3">
         <v>-600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>400</v>
       </c>
       <c r="R20" s="3">
+        <v>400</v>
+      </c>
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1580,65 +1614,68 @@
       <c r="X20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-130800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-121600</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E21" s="3">
         <v>6200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>28500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>30100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>19100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>42000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>24700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>54600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>46600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>71700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>53600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>56500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>29100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>24500</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1660,55 +1697,58 @@
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
         <v>5400</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="H22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3">
         <v>5400</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>800</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1300</v>
       </c>
       <c r="P22" s="3">
         <v>1300</v>
       </c>
       <c r="Q22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R22" s="3">
         <v>1400</v>
-      </c>
-      <c r="R22" s="3">
-        <v>1300</v>
       </c>
       <c r="S22" s="3">
         <v>1300</v>
@@ -1717,76 +1757,79 @@
         <v>1300</v>
       </c>
       <c r="U22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V22" s="3">
         <v>3200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3600</v>
-      </c>
-      <c r="X22" s="3">
-        <v>3000</v>
       </c>
       <c r="Y22" s="3">
         <v>3000</v>
       </c>
       <c r="Z22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E23" s="3">
         <v>6100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>29500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>30100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>19900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>42900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>25000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>54600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>46200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>65100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>46500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>49100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>21900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>14900</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1802,76 +1845,79 @@
       <c r="X23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>18100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-11800</v>
-      </c>
-      <c r="R24" s="3">
-        <v>500</v>
       </c>
       <c r="S24" s="3">
         <v>500</v>
       </c>
       <c r="T24" s="3">
+        <v>500</v>
+      </c>
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>700</v>
-      </c>
-      <c r="W24" s="3">
-        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
@@ -1880,10 +1926,13 @@
         <v>100</v>
       </c>
       <c r="Z24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,59 +2005,62 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E26" s="3">
         <v>4900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>21300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>31200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>40200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>34100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>47000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>36900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>36600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>14400</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>5</v>
       </c>
@@ -2024,65 +2076,68 @@
       <c r="X26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E27" s="3">
         <v>4900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>22200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>31200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>40200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>34100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>47000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>36900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>36600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>14400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>5</v>
       </c>
@@ -2098,14 +2153,17 @@
       <c r="X27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,59 +2467,62 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>300</v>
       </c>
       <c r="F32" s="3">
         <v>300</v>
       </c>
       <c r="G32" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H32" s="3">
         <v>100</v>
       </c>
       <c r="I32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3">
         <v>300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>100</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
       </c>
       <c r="L32" s="3">
+        <v>100</v>
+      </c>
+      <c r="M32" s="3">
         <v>600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>-400</v>
       </c>
       <c r="R32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2468,65 +2538,68 @@
       <c r="X32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>130800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E33" s="3">
         <v>4900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>22200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>31200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>40200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>34100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>47000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>36900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>36600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>14400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>5</v>
       </c>
@@ -2542,14 +2615,17 @@
       <c r="X33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,59 +2698,62 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E35" s="3">
         <v>4900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>22200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>31200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>40200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>34100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>47000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>36900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>36600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>16100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>14400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>5</v>
       </c>
@@ -2690,93 +2769,99 @@
       <c r="X35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,62 +2917,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>234800</v>
+      </c>
+      <c r="E41" s="3">
         <v>214400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>197500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>177700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>174200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>233200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>223100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>236900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>176800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>144500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>145200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>145700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>144600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>148800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>123800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>149200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>132900</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2905,8 +2992,11 @@
       <c r="Z41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2914,23 +3004,23 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>4900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8400</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>4500</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -2979,62 +3069,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>500</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3053,62 +3146,65 @@
       <c r="Z43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>311100</v>
+      </c>
+      <c r="E44" s="3">
         <v>301400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>297000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>294600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>273600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>268400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>254300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>269000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>294900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>292100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>286400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>292600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>272500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>246500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>208300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>170600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>136100</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3127,62 +3223,65 @@
       <c r="Z44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>13600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>11900</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>27900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>42200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>36500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>38100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>35600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>21700</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3201,62 +3300,65 @@
       <c r="Z45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>577600</v>
+      </c>
+      <c r="E46" s="3">
         <v>552800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>531000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>509300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>490500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>539800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>509300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>534600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>521000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>489800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>461200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>482300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>455100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>435100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>368000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>346400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>291300</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3275,8 +3377,11 @@
       <c r="Z46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3307,8 +3412,8 @@
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3349,62 +3454,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>705200</v>
+      </c>
+      <c r="E48" s="3">
         <v>677800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>640900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>671000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>658600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>604300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>561200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>548600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>498700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>452600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>448100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>392800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>387900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>342600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>179600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>137000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>123600</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3423,8 +3531,11 @@
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3476,8 +3587,8 @@
       <c r="S49" s="3">
         <v>11000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
+      <c r="T49" s="3">
+        <v>11000</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>5</v>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,62 +3762,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3">
         <v>19100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>21200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>23100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>25500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>28000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,62 +3916,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1318400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1264900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1206300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1209300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1177300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1176400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1105100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1113900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1045300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>965900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>939400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>907200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>877000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>814200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>586600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>495300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>426800</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3867,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,62 +4053,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E57" s="3">
         <v>59700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>68600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>73600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>67900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>62100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>63700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>58100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>55100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>53100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>62600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>58500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>62300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>54200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>51400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>30400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>30000</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3997,40 +4128,43 @@
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>55700</v>
+      </c>
+      <c r="E58" s="3">
         <v>49500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>43300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>52700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>50400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>43600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>34000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>42200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>42400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>40700</v>
-      </c>
-      <c r="M58" s="3">
-        <v>500</v>
       </c>
       <c r="N58" s="3">
         <v>500</v>
@@ -4039,20 +4173,20 @@
         <v>500</v>
       </c>
       <c r="P58" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4071,62 +4205,65 @@
       <c r="Z58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>260700</v>
+      </c>
+      <c r="E59" s="3">
         <v>286200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>247800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>241900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>221800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>296200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>197500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>217000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>197900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>202600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>312400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>365000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>363800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>390500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>349800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>306400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>259000</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4145,62 +4282,65 @@
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>434700</v>
+      </c>
+      <c r="E60" s="3">
         <v>437300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>402500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>415700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>392100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>446900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>342300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>389300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>344600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>346800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>375600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>424000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>426700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>444900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>401200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>336700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>289200</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>5</v>
       </c>
@@ -4219,62 +4359,65 @@
       <c r="Z60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>494500</v>
+      </c>
+      <c r="E61" s="3">
         <v>475400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>456200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>468900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>471500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>437300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>416500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>409800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>406800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>367500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>51900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>52000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>50300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>50500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>50600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>47800</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4293,62 +4436,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E62" s="3">
         <v>3400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>302300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>270500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>274500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>232400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>65000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>127800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>124800</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>5</v>
       </c>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,62 +4744,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>932800</v>
+      </c>
+      <c r="E66" s="3">
         <v>916100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>862600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>888700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>868000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>890700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>764900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>805400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>757700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>720800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>729700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>746400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>753100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>727600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>516800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>515100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>461700</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4663,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,62 +5158,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>183000</v>
+      </c>
+      <c r="E72" s="3">
         <v>147800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>142900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>121600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>111500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>89200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>145300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>114100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>94300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>54200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-26900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-63900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-100500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-116600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-22700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-37000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>5</v>
       </c>
@@ -5061,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,62 +5466,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>385600</v>
+      </c>
+      <c r="E76" s="3">
         <v>348800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>343700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>320600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>309300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>285600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>340200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>308500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>287600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>245100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>209700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>160800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>123900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>86500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>69800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-19800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-34900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>5</v>
       </c>
@@ -5357,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,138 +5620,144 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E81" s="3">
         <v>4900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>22200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>31200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>40200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>34100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>47000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>36900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>36600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>16100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>14400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>5</v>
       </c>
@@ -5578,14 +5773,17 @@
       <c r="X81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,68 +5810,69 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E83" s="3">
         <v>17300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8300</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>17000</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5686,8 +5885,11 @@
       <c r="Z83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,68 +6270,71 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E89" s="3">
         <v>46500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>31700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>31100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>47500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>36800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>20800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>83700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>53300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>20800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>35200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>31800</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>150400</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
@@ -6130,8 +6347,11 @@
       <c r="Z89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,68 +6378,69 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-27600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-26500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-36200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-34600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-23600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20200</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-10200</v>
       </c>
       <c r="P91" s="3">
         <v>-10200</v>
       </c>
       <c r="Q91" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="R91" s="3">
         <v>-18300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15800</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V91" s="3">
         <v>-13000</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
@@ -6232,8 +6453,11 @@
       <c r="Z91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,68 +6607,71 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-27600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-36200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-34600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-23600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-23500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16600</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-10200</v>
       </c>
       <c r="P94" s="3">
         <v>-10200</v>
       </c>
       <c r="Q94" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="R94" s="3">
         <v>-18300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-15800</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-13000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
@@ -6454,8 +6684,11 @@
       <c r="Z94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,26 +6715,27 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>200</v>
-      </c>
-      <c r="E96" s="3">
-        <v>100</v>
       </c>
       <c r="F96" s="3">
         <v>100</v>
       </c>
       <c r="G96" s="3">
+        <v>100</v>
+      </c>
+      <c r="H96" s="3">
         <v>70100</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>5</v>
       </c>
@@ -6514,8 +6748,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,68 +7021,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-70300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-400</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-100</v>
       </c>
       <c r="N100" s="3">
         <v>-100</v>
       </c>
       <c r="O100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-15900</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-98300</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
@@ -6852,8 +7098,11 @@
       <c r="Z100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6884,8 +7133,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6926,68 +7175,71 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E102" s="3">
         <v>17000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-59000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>59000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>29700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-30600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>16000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>39100</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
@@ -6998,6 +7250,9 @@
         <v>5</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="92">
   <si>
     <t>ARHS</t>
   </si>
@@ -656,262 +656,268 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>364800</v>
+      </c>
+      <c r="E8" s="3">
         <v>344600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>358400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>311400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>347000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>319100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>309800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>295200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>344000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>326200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>312900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>304600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>356300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>320000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>306300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>246300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>238200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>203300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>184000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>171300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>162800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>120500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>103400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>120700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>133800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>225700</v>
+      </c>
+      <c r="E9" s="3">
         <v>211100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>210200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>195800</v>
       </c>
-      <c r="G9" s="3">
-        <v>189500</v>
-      </c>
       <c r="H9" s="3">
+        <v>208300</v>
+      </c>
+      <c r="I9" s="3">
         <v>196100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>185400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>180100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>182000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>174500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>153000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>156600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>198300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>183700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>173200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>148600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>141300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>118500</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>5</v>
       </c>
@@ -933,65 +939,68 @@
       <c r="AB9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>139200</v>
+      </c>
+      <c r="E10" s="3">
         <v>133400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>148200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>115600</v>
       </c>
-      <c r="G10" s="3">
-        <v>157500</v>
-      </c>
       <c r="H10" s="3">
+        <v>138700</v>
+      </c>
+      <c r="I10" s="3">
         <v>123100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>124400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>115100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>162100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>151700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>159900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>148000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>158000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>136300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>133100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>97700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>96900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>84800</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1013,8 +1022,11 @@
       <c r="AB10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,8 +1055,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1123,8 +1136,11 @@
       <c r="AB12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,26 +1219,29 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1241,11 +1260,11 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
@@ -1253,12 +1272,12 @@
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>1500</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1271,8 +1290,8 @@
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1283,40 +1302,43 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>500</v>
+        <v>-1700</v>
       </c>
       <c r="E15" s="3">
         <v>500</v>
       </c>
       <c r="F15" s="3">
+        <v>500</v>
+      </c>
+      <c r="G15" s="3">
         <v>600</v>
       </c>
-      <c r="G15" s="3">
-        <v>800</v>
-      </c>
       <c r="H15" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I15" s="3">
         <v>500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>600</v>
       </c>
       <c r="J15" s="3">
         <v>600</v>
       </c>
       <c r="K15" s="3">
+        <v>600</v>
+      </c>
+      <c r="L15" s="3">
         <v>700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>500</v>
       </c>
       <c r="N15" s="3">
         <v>500</v>
@@ -1333,8 +1355,8 @@
       <c r="R15" s="3">
         <v>500</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
+      <c r="S15" s="3">
+        <v>500</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>5</v>
@@ -1351,8 +1373,8 @@
       <c r="X15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1363,8 +1385,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,65 +1415,66 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>344600</v>
+      </c>
+      <c r="E17" s="3">
         <v>328200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>311700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>305800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>319600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>308500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>280400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>276800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>303000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>302300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>258900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>259100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>291900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>272900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>256000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>223400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>242600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>186700</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1464,71 +1490,74 @@
       <c r="Z17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA17" s="3">
-        <v>0</v>
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E18" s="3">
         <v>16400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>27400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>29400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>41000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>23900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>54000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>45500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>64400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>47100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>50300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>22900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>16600</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1544,14 +1573,17 @@
       <c r="Z18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>133800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,65 +1612,66 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-300</v>
       </c>
       <c r="H20" s="3">
         <v>-300</v>
       </c>
       <c r="I20" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="J20" s="3">
         <v>-100</v>
       </c>
       <c r="K20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L20" s="3">
         <v>-300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-100</v>
       </c>
       <c r="M20" s="3">
         <v>-100</v>
       </c>
       <c r="N20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
-      </c>
-      <c r="P20" s="3">
-        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
       <c r="R20" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>400</v>
       </c>
       <c r="T20" s="3">
+        <v>400</v>
+      </c>
+      <c r="U20" s="3">
         <v>-400</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1654,71 +1687,74 @@
       <c r="Z20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-130800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-121600</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E21" s="3">
         <v>17100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>47500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6200</v>
       </c>
-      <c r="G21" s="3">
-        <v>28500</v>
-      </c>
       <c r="H21" s="3">
+        <v>25900</v>
+      </c>
+      <c r="I21" s="3">
         <v>11400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>30100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>42000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>24700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>54600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>46600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>71700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>53600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>56500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>29100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>24500</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1740,8 +1776,11 @@
       <c r="AB21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1751,50 +1790,50 @@
       <c r="E22" s="3">
         <v>1400</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3">
-        <v>5400</v>
+      <c r="F22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H22" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="I22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="J22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3">
         <v>5400</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>800</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1300</v>
       </c>
       <c r="R22" s="3">
         <v>1300</v>
       </c>
       <c r="S22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T22" s="3">
         <v>1400</v>
-      </c>
-      <c r="T22" s="3">
-        <v>1300</v>
       </c>
       <c r="U22" s="3">
         <v>1300</v>
@@ -1803,82 +1842,85 @@
         <v>1300</v>
       </c>
       <c r="W22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X22" s="3">
         <v>3200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>3600</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>3000</v>
       </c>
       <c r="AA22" s="3">
         <v>3000</v>
       </c>
       <c r="AB22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E23" s="3">
         <v>17400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>47700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>29500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>30100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>19900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>42900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>25000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>54600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>46200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>65100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>46500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>49100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>21900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>14900</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1894,82 +1936,85 @@
       <c r="Z23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0</v>
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E24" s="3">
         <v>5200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>18100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-11800</v>
-      </c>
-      <c r="T24" s="3">
-        <v>500</v>
       </c>
       <c r="U24" s="3">
         <v>500</v>
       </c>
       <c r="V24" s="3">
+        <v>500</v>
+      </c>
+      <c r="W24" s="3">
         <v>700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>700</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>100</v>
       </c>
       <c r="Z24" s="3">
         <v>100</v>
@@ -1978,10 +2023,13 @@
         <v>100</v>
       </c>
       <c r="AB24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,65 +2108,68 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E26" s="3">
         <v>12200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>35100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>22200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>31200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>40200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>34100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>47000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>36900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>36600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>14400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>5</v>
       </c>
@@ -2134,71 +2185,74 @@
       <c r="Z26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA26" s="3">
-        <v>0</v>
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E27" s="3">
         <v>12200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>35100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>22200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>31200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>40200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>34100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>47000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>36900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>36600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>16100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>14400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>5</v>
       </c>
@@ -2214,14 +2268,17 @@
       <c r="Z27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2357,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2440,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,65 +2606,68 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>300</v>
       </c>
       <c r="H32" s="3">
         <v>300</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J32" s="3">
         <v>100</v>
       </c>
       <c r="K32" s="3">
+        <v>100</v>
+      </c>
+      <c r="L32" s="3">
         <v>300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>100</v>
       </c>
       <c r="M32" s="3">
         <v>100</v>
       </c>
       <c r="N32" s="3">
+        <v>100</v>
+      </c>
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
       <c r="R32" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>-400</v>
       </c>
       <c r="T32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="U32" s="3">
         <v>400</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2614,71 +2683,74 @@
       <c r="Z32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>130800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E33" s="3">
         <v>12200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>35100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>22200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>31200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>40200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>34100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>47000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>36900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>36600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>16100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>14400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>5</v>
       </c>
@@ -2694,14 +2766,17 @@
       <c r="Z33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,65 +2855,68 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E35" s="3">
         <v>12200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>35100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>22200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>31200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>40200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>34100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>47000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>36900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>36600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>16100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>14400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>5</v>
       </c>
@@ -2854,99 +2932,105 @@
       <c r="Z35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,68 +3090,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>253400</v>
+      </c>
+      <c r="E41" s="3">
         <v>262200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>234800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>214400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>197500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>177700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>174200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>233200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>223100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>236900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>176800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>144500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>145200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>145700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>144600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>148800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>123800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>149200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>132900</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>5</v>
       </c>
@@ -3085,13 +3171,16 @@
       <c r="AB41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -3100,23 +3189,23 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>4900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8400</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>4500</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3165,68 +3254,71 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>500</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3245,68 +3337,71 @@
       <c r="AB43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>338800</v>
+      </c>
+      <c r="E44" s="3">
         <v>328700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>311100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>301400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>297000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>294600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>273600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>268400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>254300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>269000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>294900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>292100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>286400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>292600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>272500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>246500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>208300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>170600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>136100</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3325,13 +3420,16 @@
       <c r="AB44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="3">
+        <v>13300</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>5</v>
@@ -3339,54 +3437,54 @@
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>13600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>11900</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P45" s="3">
         <v>27900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>42200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>36500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>38100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>35600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>26300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>21700</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3405,68 +3503,71 @@
       <c r="AB45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>621400</v>
+      </c>
+      <c r="E46" s="3">
         <v>626200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>577600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>552800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>531000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>509300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>490500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>539800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>509300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>534600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>521000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>489800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>461200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>482300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>455100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>435100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>368000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>346400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>291300</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3485,8 +3586,11 @@
       <c r="AB46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3523,8 +3627,8 @@
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3565,68 +3669,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>740800</v>
+      </c>
+      <c r="E48" s="3">
         <v>728800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>705200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>677800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>640900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>671000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>658600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>604300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>561200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>548600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>498700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>452600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>448100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>392800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>387900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>342600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>179600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>137000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>123600</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3645,8 +3752,11 @@
       <c r="AB48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3704,8 +3814,8 @@
       <c r="U49" s="3">
         <v>11000</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>5</v>
+      <c r="V49" s="3">
+        <v>11000</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>5</v>
@@ -3725,8 +3835,11 @@
       <c r="AB49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,68 +4001,71 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E52" s="3">
         <v>2000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3">
         <v>19100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>21200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>23100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>25500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>28000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1000</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3965,8 +4084,11 @@
       <c r="AB52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,68 +4167,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1394700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1378600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1318400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1264900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1206300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1209300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1177300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1176400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1105100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1113900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1045300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>965900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>939400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>907200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>877000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>814200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>586600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>495300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>426800</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>5</v>
       </c>
@@ -4125,8 +4250,11 @@
       <c r="AB54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,68 +4314,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>78400</v>
+      </c>
+      <c r="E57" s="3">
         <v>69500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>70500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>59700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>68600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>73600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>67900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>62100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>63700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>58100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>55100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>53100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>62600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>58500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>62300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>54200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>51400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>30400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>30000</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4265,46 +4395,49 @@
       <c r="AB57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E58" s="3">
         <v>63100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>55700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>49500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>43300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>52700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>50400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>43600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>34000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>42200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>42400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>40700</v>
-      </c>
-      <c r="O58" s="3">
-        <v>500</v>
       </c>
       <c r="P58" s="3">
         <v>500</v>
@@ -4313,20 +4446,20 @@
         <v>500</v>
       </c>
       <c r="R58" s="3">
+        <v>500</v>
+      </c>
+      <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4345,68 +4478,71 @@
       <c r="AB58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>264300</v>
+      </c>
+      <c r="E59" s="3">
         <v>278000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>260700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>286200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>247800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>241900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>221800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>296200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>197500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>217000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>197900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>202600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>312400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>365000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>363800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>390500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>349800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>306400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>259000</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4425,68 +4561,71 @@
       <c r="AB59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>453300</v>
+      </c>
+      <c r="E60" s="3">
         <v>466200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>434700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>437300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>402500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>415700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>392100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>446900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>342300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>389300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>344600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>346800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>375600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>424000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>426700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>444900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>401200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>336700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>289200</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>5</v>
       </c>
@@ -4505,68 +4644,71 @@
       <c r="AB60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>519600</v>
+      </c>
+      <c r="E61" s="3">
         <v>508500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>494500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>475400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>456200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>468900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>471500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>437300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>416500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>409800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>406800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>367500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>51800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>51900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>52000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>50300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>50500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>50600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>47800</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4585,68 +4727,71 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E62" s="3">
         <v>3600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>302300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>270500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>274500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>232400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>65000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>127800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>124800</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>5</v>
       </c>
@@ -4665,8 +4810,11 @@
       <c r="AB62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,68 +5059,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>976500</v>
+      </c>
+      <c r="E66" s="3">
         <v>978200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>932800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>916100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>862600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>888700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>868000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>890700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>764900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>805400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>757700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>720800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>729700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>746400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>753100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>727600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>516800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>515100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>461700</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4985,8 +5142,11 @@
       <c r="AB66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,68 +5505,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>210400</v>
+      </c>
+      <c r="E72" s="3">
         <v>195300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>183000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>147800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>142900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>121600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>111500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>89200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>145300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>114100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>94300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>54200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-63900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-100500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-116600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-22700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-37000</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>5</v>
       </c>
@@ -5415,8 +5588,11 @@
       <c r="AB72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,68 +5837,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>418200</v>
+      </c>
+      <c r="E76" s="3">
         <v>400400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>385600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>348800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>343700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>320600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>309300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>285600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>340200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>308500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>287600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>245100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>209700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>160800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>123900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>86500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>69800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-19800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-34900</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>5</v>
       </c>
@@ -5735,8 +5920,11 @@
       <c r="AB76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,150 +6003,156 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E81" s="3">
         <v>12200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>35100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>22200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>31200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>40200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>34100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>47000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>36900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>36600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>16100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>14400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>5</v>
       </c>
@@ -5974,14 +6168,17 @@
       <c r="Z81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,74 +6207,75 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E83" s="3">
         <v>19700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>15900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8300</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>17000</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>5</v>
       </c>
@@ -6090,8 +6288,11 @@
       <c r="AB83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,74 +6703,77 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E89" s="3">
         <v>46100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>34900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>46500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>31700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>31100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>47500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>36800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>20800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>83700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>53300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>20800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>35200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>31800</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>150400</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>5</v>
       </c>
@@ -6570,8 +6786,11 @@
       <c r="AB89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,8 +6819,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6609,65 +6829,65 @@
         <v>-18100</v>
       </c>
       <c r="E91" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-14000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-34600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-23600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-23500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-20200</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-10200</v>
       </c>
       <c r="R91" s="3">
         <v>-10200</v>
       </c>
       <c r="S91" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="T91" s="3">
         <v>-18300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15800</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-13000</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>5</v>
       </c>
@@ -6680,8 +6900,11 @@
       <c r="AB91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,8 +7066,11 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6849,65 +7078,65 @@
         <v>-18100</v>
       </c>
       <c r="E94" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-14000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-26500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-36200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-34600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-23600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16600</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-10200</v>
       </c>
       <c r="R94" s="3">
         <v>-10200</v>
       </c>
       <c r="S94" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="T94" s="3">
         <v>-18300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-15800</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-13000</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>5</v>
       </c>
@@ -6920,8 +7149,11 @@
       <c r="AB94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,32 +7182,33 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>100</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>200</v>
-      </c>
-      <c r="G96" s="3">
-        <v>100</v>
       </c>
       <c r="H96" s="3">
         <v>100</v>
       </c>
       <c r="I96" s="3">
+        <v>100</v>
+      </c>
+      <c r="J96" s="3">
         <v>70100</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
@@ -6988,8 +7221,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7030,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,8 +7512,11 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7279,65 +7524,65 @@
         <v>-600</v>
       </c>
       <c r="E100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-70300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-400</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-100</v>
       </c>
       <c r="P100" s="3">
         <v>-100</v>
       </c>
       <c r="Q100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-15900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-98300</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>5</v>
       </c>
@@ -7350,8 +7595,11 @@
       <c r="AB100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7388,8 +7636,8 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7430,74 +7678,77 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E102" s="3">
         <v>27400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>17000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>20000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-59000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>59000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>29700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>25100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-30600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>16000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>39100</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>5</v>
       </c>
@@ -7508,6 +7759,9 @@
         <v>5</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARHS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="92">
   <si>
     <t>ARHS</t>
   </si>
@@ -656,271 +656,278 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>314300</v>
+      </c>
+      <c r="E8" s="3">
         <v>364800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>344600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>358400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>311400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>347000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>319100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>309800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>295200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>344000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>326200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>312900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>304600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>356300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>320000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>306300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>246300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>238200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>203300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>184000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>171300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>162800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>120500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>103400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>120700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>133800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>199800</v>
+      </c>
+      <c r="E9" s="3">
         <v>225700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>211100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>210200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>195800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>208300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>196100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>185400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>180100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>182000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>174500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>153000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>156600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>198300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>183700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>173200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>148600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>141300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>118500</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
@@ -942,68 +949,71 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>114400</v>
+      </c>
+      <c r="E10" s="3">
         <v>139200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>133400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>148200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>115600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>138700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>123100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>124400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>115100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>162100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>151700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>159900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>148000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>158000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>136300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>133100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>97700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>96900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>84800</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1025,8 +1035,11 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,8 +1069,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1139,8 +1153,11 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,29 +1239,32 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1200</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1263,11 +1283,11 @@
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
@@ -1275,12 +1295,12 @@
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>1500</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1293,8 +1313,8 @@
       <c r="Y14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1305,43 +1325,46 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>-1700</v>
-      </c>
-      <c r="E15" s="3">
-        <v>500</v>
       </c>
       <c r="F15" s="3">
         <v>500</v>
       </c>
       <c r="G15" s="3">
+        <v>500</v>
+      </c>
+      <c r="H15" s="3">
         <v>600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>-1800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>600</v>
       </c>
       <c r="L15" s="3">
+        <v>600</v>
+      </c>
+      <c r="M15" s="3">
         <v>700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>500</v>
       </c>
       <c r="O15" s="3">
         <v>500</v>
@@ -1358,8 +1381,8 @@
       <c r="S15" s="3">
         <v>500</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
+      <c r="T15" s="3">
+        <v>500</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>5</v>
@@ -1376,8 +1399,8 @@
       <c r="Y15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1388,8 +1411,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,68 +1442,69 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>312000</v>
+      </c>
+      <c r="E17" s="3">
         <v>344600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>328200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>311700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>305800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>319600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>308500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>280400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>276800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>303000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>302300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>258900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>259100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>291900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>272900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>256000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>223400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>242600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>186700</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1493,74 +1520,77 @@
       <c r="AA17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB17" s="3">
-        <v>0</v>
+      <c r="AB17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E18" s="3">
         <v>20300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>46800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>27400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>29400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>41000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>23900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>54000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>45500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>64400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>47100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>50300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>22900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>16600</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1576,14 +1606,17 @@
       <c r="AA18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC18" s="3">
         <v>133800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>124800</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,68 +1646,69 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-300</v>
       </c>
       <c r="I20" s="3">
         <v>-300</v>
       </c>
       <c r="J20" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
       </c>
       <c r="L20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M20" s="3">
         <v>-300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-100</v>
       </c>
       <c r="N20" s="3">
         <v>-100</v>
       </c>
       <c r="O20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>700</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>400</v>
       </c>
       <c r="U20" s="3">
+        <v>400</v>
+      </c>
+      <c r="V20" s="3">
         <v>-400</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1690,74 +1724,77 @@
       <c r="AA20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-130800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-121600</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E21" s="3">
         <v>18300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>47500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>25900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>30100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>19100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>42000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>24700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>54600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>46600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>71700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>53600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>56500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>29100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>24500</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1779,13 +1816,16 @@
       <c r="AC21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>1400</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E22" s="3">
         <v>1400</v>
@@ -1793,50 +1833,50 @@
       <c r="F22" s="3">
         <v>1400</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="G22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3">
         <v>1300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1400</v>
       </c>
       <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="K22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3">
         <v>5400</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>800</v>
-      </c>
-      <c r="R22" s="3">
-        <v>1300</v>
       </c>
       <c r="S22" s="3">
         <v>1300</v>
       </c>
       <c r="T22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U22" s="3">
         <v>1400</v>
-      </c>
-      <c r="U22" s="3">
-        <v>1300</v>
       </c>
       <c r="V22" s="3">
         <v>1300</v>
@@ -1845,85 +1885,88 @@
         <v>1300</v>
       </c>
       <c r="X22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Y22" s="3">
         <v>3200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3600</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>3000</v>
       </c>
       <c r="AB22" s="3">
         <v>3000</v>
       </c>
       <c r="AC22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E23" s="3">
         <v>20900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>17400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>47700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>29500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>30100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>19900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>42900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>25000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>54600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>46200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>65100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>46500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>49100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>21900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>14900</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1939,85 +1982,88 @@
       <c r="AA23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB23" s="3">
-        <v>0</v>
+      <c r="AB23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>5800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>18100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-11800</v>
-      </c>
-      <c r="U24" s="3">
-        <v>500</v>
       </c>
       <c r="V24" s="3">
         <v>500</v>
       </c>
       <c r="W24" s="3">
+        <v>500</v>
+      </c>
+      <c r="X24" s="3">
         <v>700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>700</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>100</v>
       </c>
       <c r="AA24" s="3">
         <v>100</v>
@@ -2026,10 +2072,13 @@
         <v>100</v>
       </c>
       <c r="AC24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,68 +2160,71 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E26" s="3">
         <v>15100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>35100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>21300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>22200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>31200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>40200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>34100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>47000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>36900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>36600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>14400</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>5</v>
       </c>
@@ -2188,74 +2240,77 @@
       <c r="AA26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB26" s="3">
-        <v>0</v>
+      <c r="AB26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E27" s="3">
         <v>15100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>35100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>22200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>15100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>31200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>40200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>34100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>47000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>36900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>36600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>14400</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>5</v>
       </c>
@@ -2271,14 +2326,17 @@
       <c r="AA27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB27" s="3">
-        <v>0</v>
+      <c r="AB27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2443,8 +2504,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,68 +2676,71 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>300</v>
       </c>
       <c r="I32" s="3">
         <v>300</v>
       </c>
       <c r="J32" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
       </c>
       <c r="L32" s="3">
+        <v>100</v>
+      </c>
+      <c r="M32" s="3">
         <v>300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>100</v>
       </c>
       <c r="N32" s="3">
         <v>100</v>
       </c>
       <c r="O32" s="3">
+        <v>100</v>
+      </c>
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-700</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>-400</v>
       </c>
       <c r="U32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V32" s="3">
         <v>400</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2686,74 +2756,77 @@
       <c r="AA32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC32" s="3">
         <v>130800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E33" s="3">
         <v>15100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>35100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>22200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>15100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>31200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>40200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>34100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>47000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>36900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>36600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>14400</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>5</v>
       </c>
@@ -2769,14 +2842,17 @@
       <c r="AA33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB33" s="3">
-        <v>0</v>
+      <c r="AB33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,68 +2934,71 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E35" s="3">
         <v>15100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>35100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>22200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>15100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>31200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>40200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>34100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>47000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>36900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>36600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>14400</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>5</v>
       </c>
@@ -2935,102 +3014,108 @@
       <c r="AA35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
+      <c r="AB35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,71 +3177,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>177100</v>
+      </c>
+      <c r="E41" s="3">
         <v>253400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>262200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>234800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>214400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>197500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>177700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>174200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>233200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>223100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>236900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>176800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>144500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>145200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>145700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>144600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>148800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>123800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>149200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>132900</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>5</v>
       </c>
@@ -3174,17 +3261,20 @@
       <c r="AC41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>4200</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -3192,23 +3282,23 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>4900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8400</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>4500</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -3257,71 +3347,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>500</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3340,71 +3433,74 @@
       <c r="AC43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>369500</v>
+      </c>
+      <c r="E44" s="3">
         <v>338800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>328700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>311100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>301400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>297000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>294600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>273600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>268400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>254300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>269000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>294900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>292100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>286400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>292600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>272500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>246500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>208300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>170600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>136100</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3423,71 +3519,74 @@
       <c r="AC44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>13300</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>13600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>11900</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="3">
         <v>27900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>42200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>36500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>38100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>35600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>26300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>21700</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3506,71 +3605,74 @@
       <c r="AC45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>581800</v>
+      </c>
+      <c r="E46" s="3">
         <v>621400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>626200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>577600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>552800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>531000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>509300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>490500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>539800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>509300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>534600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>521000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>489800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>461200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>482300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>455100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>435100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>368000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>346400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>291300</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3589,8 +3691,11 @@
       <c r="AC46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3630,8 +3735,8 @@
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3672,71 +3777,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>763500</v>
+      </c>
+      <c r="E48" s="3">
         <v>740800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>728800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>705200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>677800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>640900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>671000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>658600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>604300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>561200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>548600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>498700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>452600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>448100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>392800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>387900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>342600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>179600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>137000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>123600</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3755,8 +3863,11 @@
       <c r="AC48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3817,8 +3928,8 @@
       <c r="V49" s="3">
         <v>11000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
+      <c r="W49" s="3">
+        <v>11000</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>5</v>
@@ -3838,8 +3949,11 @@
       <c r="AC49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,71 +4121,74 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="3">
         <v>19100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>21200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>23100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>25500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>28000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4087,8 +4207,11 @@
       <c r="AC52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,71 +4293,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1377500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1394700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1378600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1318400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1264900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1206300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1209300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1177300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1176400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1105100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1113900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1045300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>965900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>939400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>907200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>877000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>814200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>586600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>495300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>426800</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>5</v>
       </c>
@@ -4253,8 +4379,11 @@
       <c r="AC54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,71 +4445,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E57" s="3">
         <v>78400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>69500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>70500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>59700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>68600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>73600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>67900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>62100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>63700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>58100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>55100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>53100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>62600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>58500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>62300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>54200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>51400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>30400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>30000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4398,49 +4529,52 @@
       <c r="AC57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>65400</v>
+      </c>
+      <c r="E58" s="3">
         <v>61000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>63100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>55700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>49500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>43300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>52700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>50400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>43600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>34000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>42200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>42400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>40700</v>
-      </c>
-      <c r="P58" s="3">
-        <v>500</v>
       </c>
       <c r="Q58" s="3">
         <v>500</v>
@@ -4449,20 +4583,20 @@
         <v>500</v>
       </c>
       <c r="S58" s="3">
+        <v>500</v>
+      </c>
+      <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4481,71 +4615,74 @@
       <c r="AC58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>285100</v>
+      </c>
+      <c r="E59" s="3">
         <v>264300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>278000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>260700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>286200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>247800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>241900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>221800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>296200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>197500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>217000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>197900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>202600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>312400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>365000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>363800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>390500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>349800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>306400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>259000</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4564,71 +4701,74 @@
       <c r="AC59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>466400</v>
+      </c>
+      <c r="E60" s="3">
         <v>453300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>466200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>434700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>437300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>402500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>415700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>392100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>446900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>342300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>389300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>344600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>346800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>375600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>424000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>426700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>444900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>401200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>336700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>289200</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>5</v>
       </c>
@@ -4647,71 +4787,74 @@
       <c r="AC60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>534300</v>
+      </c>
+      <c r="E61" s="3">
         <v>519600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>508500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>494500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>475400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>456200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>468900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>471500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>437300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>416500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>409800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>406800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>367500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>51800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>51900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>52000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>50300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>50500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>50600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>47800</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4730,71 +4873,74 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E62" s="3">
         <v>3700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>302300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>270500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>274500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>232400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>65000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>127800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>124800</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>5</v>
       </c>
@@ -4813,8 +4959,11 @@
       <c r="AC62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,71 +5217,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1004800</v>
+      </c>
+      <c r="E66" s="3">
         <v>976500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>978200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>932800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>916100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>862600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>888700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>868000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>890700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>764900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>805400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>757700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>720800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>729700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>746400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>753100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>727600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>516800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>515100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>461700</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>5</v>
       </c>
@@ -5145,8 +5303,11 @@
       <c r="AC66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5425,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,71 +5679,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>162200</v>
+      </c>
+      <c r="E72" s="3">
         <v>210400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>195300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>183000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>147800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>142900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>121600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>111500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>89200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>145300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>114100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>94300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>54200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-26900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-63900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-100500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-116600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-22700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-37000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>5</v>
       </c>
@@ -5591,8 +5765,11 @@
       <c r="AC72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,71 +6023,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>372700</v>
+      </c>
+      <c r="E76" s="3">
         <v>418200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>400400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>385600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>348800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>343700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>320600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>309300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>285600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>340200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>308500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>287600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>245100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>209700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>160800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>123900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>86500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>69800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-19800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-34900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>5</v>
       </c>
@@ -5923,8 +6109,11 @@
       <c r="AC76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,156 +6195,162 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E81" s="3">
         <v>15100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>35100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>22200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>15100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>31200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>40200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>34100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>47000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>36900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>36600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>14400</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>5</v>
       </c>
@@ -6171,14 +6366,17 @@
       <c r="AA81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB81" s="3">
-        <v>0</v>
+      <c r="AB81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,77 +6406,78 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E83" s="3">
         <v>20700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>19700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>17300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>15900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>6700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>8300</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3">
         <v>17000</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>5</v>
       </c>
@@ -6291,8 +6490,11 @@
       <c r="AC83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,77 +6920,80 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E89" s="3">
         <v>9300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>46100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>34900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>46500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>31700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>31100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>47500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>36800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>20800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>83700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>53300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>20800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>35200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>31800</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3">
         <v>150400</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>5</v>
       </c>
@@ -6789,8 +7006,11 @@
       <c r="AC89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,77 +7040,78 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-18100</v>
+        <v>-16900</v>
       </c>
       <c r="E91" s="3">
         <v>-18100</v>
       </c>
       <c r="F91" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-14000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-25900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-34600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-23600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-20200</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-10200</v>
       </c>
       <c r="S91" s="3">
         <v>-10200</v>
       </c>
       <c r="T91" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="U91" s="3">
         <v>-18300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-15800</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>5</v>
       </c>
@@ -6903,8 +7124,11 @@
       <c r="AC91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,77 +7296,80 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-18100</v>
+        <v>-15900</v>
       </c>
       <c r="E94" s="3">
         <v>-18100</v>
       </c>
       <c r="F94" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="G94" s="3">
         <v>-14000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-36200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-34600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-16600</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-10200</v>
       </c>
       <c r="S94" s="3">
         <v>-10200</v>
       </c>
       <c r="T94" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="U94" s="3">
         <v>-18300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-15800</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>5</v>
       </c>
@@ -7152,8 +7382,11 @@
       <c r="AC94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,35 +7416,36 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>100</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>200</v>
-      </c>
-      <c r="H96" s="3">
-        <v>100</v>
       </c>
       <c r="I96" s="3">
         <v>100</v>
       </c>
       <c r="J96" s="3">
+        <v>100</v>
+      </c>
+      <c r="K96" s="3">
         <v>70100</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
@@ -7224,8 +7458,8 @@
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7266,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,77 +7758,80 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-600</v>
+        <v>-50600</v>
       </c>
       <c r="E100" s="3">
         <v>-600</v>
       </c>
       <c r="F100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G100" s="3">
         <v>-400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-70300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-400</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-100</v>
       </c>
       <c r="Q100" s="3">
         <v>-100</v>
       </c>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-15900</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-98300</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>5</v>
       </c>
@@ -7598,8 +7844,11 @@
       <c r="AC100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7639,8 +7888,8 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7681,77 +7930,80 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-76100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>27400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>20500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>17000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>20000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-59000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>59000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>29700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>25100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-30600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>16000</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3">
         <v>39100</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>5</v>
       </c>
@@ -7762,6 +8014,9 @@
         <v>5</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
